--- a/utils/monday_sprint_sprint_2026-11.xlsx
+++ b/utils/monday_sprint_sprint_2026-11.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="453">
   <si>
     <t>Ticket</t>
   </si>
@@ -87,7 +87,7 @@
     <t>17/03/2026</t>
   </si>
   <si>
-    <t>23/04/2026</t>
+    <t>22/04/2026</t>
   </si>
   <si>
     <t>Feito</t>
@@ -129,9 +129,6 @@
     <t>10/03/2026</t>
   </si>
   <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -150,6 +147,9 @@
     <t>06/03/2026</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
@@ -450,324 +450,312 @@
     <t>Bloco K - Integração dados Altona / Benner.</t>
   </si>
   <si>
-    <t>Prezado, bom dia. Situação: Atualmente a integração dos dados Altona / Benner, para integrar o bloco K, precisa da intervenção de uma pessoa para disparar a rotina. Necessidade: Automatizar este processo. Ação: 1. Implementar status indicando que o dado está pronto para ser enviado para Benner. 2. A</t>
+    <t>Coleta e identificação de sequencia</t>
+  </si>
+  <si>
+    <t>37032</t>
+  </si>
+  <si>
+    <t>NOVOS INDICADORES BI - Reunião</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria da criação de um relatório BI para controle de Análise Crítica, Alertas de revisões, Pré-Análise e Procedimentos, gostaria de deixar mais visual e para que seja atualizado constantemente. Acredito que seria interessante se pudéssemos marcar uma reunião para apresentar a forma que</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>37105</t>
+  </si>
+  <si>
+    <t>Melhoria na tela de baixa de ordens preventivas e corretivas</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos implementar uma melhoria no sistema, a ideia é deixarmos um botão disponível na tela de baixa de ordens tanto preventivas quanto corretivas. Hoje estamos utilizando a opção de anexos do equipamento: A Ideia é que nas telas de baixa de ordens (são as telas que os mantenedores ma</t>
+  </si>
+  <si>
+    <t>Implementar Alerta de Solicitações de serviço com status de aguardando programação</t>
+  </si>
+  <si>
+    <t>36968</t>
+  </si>
+  <si>
+    <t>ADICIONAR MOTIVO DE PARADA - C. PARADA - 232 / DESCRIÇÃO - TROCA DE GÁS</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito adicionar; C. Parada Descrição 232 TROCA DE GÁS. MOTIVO: O soldador de produção, leva um tempo considerável para fazer o Setup e precisamos estratificar este tempo para avaliar a eficiência. At.te,</t>
+  </si>
+  <si>
+    <t>Juliano Carriel</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>37530</t>
+  </si>
+  <si>
+    <t>Layout ofertas exportação</t>
+  </si>
+  <si>
+    <t>37563</t>
+  </si>
+  <si>
+    <t>Corridas Fora de Liga</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos que esse relatório gere a opção de excel. Com as informações de Forno, Corrida, Liga, Faixa Mínima, Faixa Máxima e mensurado Local onde pode ser adicionado o botão, após colocar as informações de ano e forno abre essa tela, e nessa tela incluir um botão para gerar um excel de t</t>
+  </si>
+  <si>
+    <t>Espectrometria</t>
+  </si>
+  <si>
+    <t>Implementar Alerta Ordens de serviços com data de programação (já programadas) e não foram executadas</t>
+  </si>
+  <si>
+    <t>36467</t>
+  </si>
+  <si>
+    <t>Sitema retrabalho ajustagem com erro</t>
+  </si>
+  <si>
+    <t>Boa tarde! Enviando para o Email correto. Gentileza considerar o e-mail abaixo. Atenciosamente, De: Fernanda da Costa Rodrigues Enviada em: quarta-feira, 4 de fevereiro de 2026 14:25 Para: 'Suporte Altona' Cc: Edson João Hammermeister ; Lucas José Sebold Assunto: RES: Resolvido: Sitema retrabalho aj</t>
+  </si>
+  <si>
+    <t>Fernanda da Costa Rodrigues</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>37461</t>
+  </si>
+  <si>
+    <t>Altona || Adiantamento de Clientes do Exterior - Relatório de Variação Cambial - (Reunião)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solicito a criação de uma rotina e posteriormente de um relatório que faça a demonstração da variação cambial dos adiantamentos de clientes do exterior. Para isso é preciso: 1) Criar um campo para cadastrar a moeda e sua respectiva cotação. Essa cotação será alimentada manualmente. Exemplo: Dólar – </t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>37475</t>
+  </si>
+  <si>
+    <t>BOTÃO ALTERAÇÃO DE TEMPO SIMULTÂNEA</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor criar um botão na tela UCPP11 que possibilite incluir o tempo em mais de um setor selecionado. OBS: Ideia alinhada com o Sr. Sandro Schram. Qualquer dúvida, estou à disposição. Obrigada, At.te</t>
+  </si>
+  <si>
+    <t>Karolina Moreira da Silva</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>36232</t>
+  </si>
+  <si>
+    <t>Report técnico - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
+    <t>23/01/2026</t>
+  </si>
+  <si>
+    <t>33631</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - Custos</t>
+  </si>
+  <si>
+    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
+  </si>
+  <si>
+    <t>Marcelo Americo</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>20/08/2025</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>30069</t>
+  </si>
+  <si>
+    <t>Controle de Importação - integração financeira</t>
+  </si>
+  <si>
+    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>11/02/2025</t>
+  </si>
+  <si>
+    <t>36219</t>
+  </si>
+  <si>
+    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
+  </si>
+  <si>
+    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>Como teremos 3 modelagens as op’s poderão ter quantidades diferentes nas modelagens, validar com o pessoal do APS essa interligação.</t>
+  </si>
+  <si>
+    <t>36335</t>
+  </si>
+  <si>
+    <t>Ajuste em gráficos no B.I</t>
+  </si>
+  <si>
+    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>36541</t>
+  </si>
+  <si>
+    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>36728</t>
+  </si>
+  <si>
+    <t>Aplicação QlikSense - Custeio FTF</t>
+  </si>
+  <si>
+    <t>Bom dia Felipe. Desenvolver um QVD para aplicação que possamos consultar custo FTF, semelhante informações do relatório FTF anexo.</t>
+  </si>
+  <si>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>37498</t>
+  </si>
+  <si>
+    <t>Alteração sistema registro USE-ULE Windows</t>
+  </si>
+  <si>
+    <t>Bom dia, Necessitamos que seja alterado a forma que os registros da moldagem são exibidos ao clicar no botão "Imprime Registro". Atualmente ao clicar no botão recebemos as informações com as respostas dos setores de preparação, moldagem, fechamento e desmoldagem, deixando de fora o setor da macharia</t>
+  </si>
+  <si>
+    <t>João Eduardo Zarth</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>37288</t>
+  </si>
+  <si>
+    <t>melhoria no sistema de inventário das embalagens</t>
+  </si>
+  <si>
+    <t>Bom dia! Com o aval do Rafael, solicito uma melhoria no sistema de inventário das embalagens (caixas Magayver). Atualmente, o sistema considera apenas as embalagens contadas fisicamente. Porém, existe a possibilidade de haver saldo no sistema mesmo quando a embalagem não existe fisicamente. Diante d</t>
+  </si>
+  <si>
+    <t>36430</t>
+  </si>
+  <si>
+    <t>Indicadores de Setup - IROG Usinagem</t>
+  </si>
+  <si>
+    <t>________________________________ De: Pedro Henrique Poburko Enviado: terça-feira, 3 de fevereiro de 2026 14:06 Para: Suporte Altona Assunto: RE: Resolvido: Indicadores de Setup - IROG Usinagem Felipe, bom dia. Precisamos que o tempo de entrega do indicador abaixo seja removido. Consegue alterar, por</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Poburko</t>
+  </si>
+  <si>
+    <t>03/02/2026</t>
+  </si>
+  <si>
+    <t>36218</t>
+  </si>
+  <si>
+    <t>Melhoria Aplicação QlikSense - Custeio Valor</t>
+  </si>
+  <si>
+    <t>Felipe bom dia! Importar para aplicação de Custeio planilhas Excel com a base de ajustes gerenciais, concatenando com o QVD de extração de dados diretamente do Sistema de Custeio.</t>
+  </si>
+  <si>
+    <t>37514</t>
+  </si>
+  <si>
+    <t>Melhoria cadastro de matérias</t>
+  </si>
+  <si>
+    <t>Boa tarde, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1. Gostaria de solicitar a implementação de um campo no sistema que permita a geração de uma planilha em Excel antes da aprovação do cadastro. Att,</t>
+  </si>
+  <si>
+    <t>Vanessa Knoth</t>
+  </si>
+  <si>
+    <t>36206</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web (copy)</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>37526</t>
+  </si>
+  <si>
+    <t>PDI - Relatório de apontamentos</t>
+  </si>
+  <si>
+    <t>Verificar a situação apresentada pelo usuário Gerson Mendonça: Atenciosamente,</t>
   </si>
   <si>
     <t>Alexandre Longo</t>
   </si>
   <si>
-    <t>18/02/2026</t>
-  </si>
-  <si>
-    <t>Coleta e identificação de sequencia</t>
-  </si>
-  <si>
-    <t>37032</t>
-  </si>
-  <si>
-    <t>NOVOS INDICADORES BI - Reunião</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria da criação de um relatório BI para controle de Análise Crítica, Alertas de revisões, Pré-Análise e Procedimentos, gostaria de deixar mais visual e para que seja atualizado constantemente. Acredito que seria interessante se pudéssemos marcar uma reunião para apresentar a forma que</t>
-  </si>
-  <si>
-    <t>04/03/2026</t>
-  </si>
-  <si>
-    <t>37105</t>
-  </si>
-  <si>
-    <t>Melhoria na tela de baixa de ordens preventivas e corretivas</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos implementar uma melhoria no sistema, a ideia é deixarmos um botão disponível na tela de baixa de ordens tanto preventivas quanto corretivas. Hoje estamos utilizando a opção de anexos do equipamento: A Ideia é que nas telas de baixa de ordens (são as telas que os mantenedores ma</t>
-  </si>
-  <si>
-    <t>Implementar Alerta de Solicitações de serviço com status de aguardando programação</t>
-  </si>
-  <si>
-    <t>36968</t>
-  </si>
-  <si>
-    <t>ADICIONAR MOTIVO DE PARADA - C. PARADA - 232 / DESCRIÇÃO - TROCA DE GÁS</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito adicionar; C. Parada Descrição 232 TROCA DE GÁS. MOTIVO: O soldador de produção, leva um tempo considerável para fazer o Setup e precisamos estratificar este tempo para avaliar a eficiência. At.te,</t>
-  </si>
-  <si>
-    <t>Juliano Carriel</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
-    <t>37530</t>
-  </si>
-  <si>
-    <t>Layout ofertas exportação</t>
-  </si>
-  <si>
-    <t>37563</t>
-  </si>
-  <si>
-    <t>Corridas Fora de Liga</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos que esse relatório gere a opção de excel. Com as informações de Forno, Corrida, Liga, Faixa Mínima, Faixa Máxima e mensurado Local onde pode ser adicionado o botão, após colocar as informações de ano e forno abre essa tela, e nessa tela incluir um botão para gerar um excel de t</t>
-  </si>
-  <si>
-    <t>Espectrometria</t>
-  </si>
-  <si>
-    <t>Implementar Alerta Ordens de serviços com data de programação (já programadas) e não foram executadas</t>
-  </si>
-  <si>
-    <t>36467</t>
-  </si>
-  <si>
-    <t>Sitema retrabalho ajustagem com erro</t>
-  </si>
-  <si>
-    <t>Boa tarde! Enviando para o Email correto. Gentileza considerar o e-mail abaixo. Atenciosamente, De: Fernanda da Costa Rodrigues Enviada em: quarta-feira, 4 de fevereiro de 2026 14:25 Para: 'Suporte Altona' Cc: Edson João Hammermeister ; Lucas José Sebold Assunto: RES: Resolvido: Sitema retrabalho aj</t>
-  </si>
-  <si>
-    <t>Fernanda da Costa Rodrigues</t>
-  </si>
-  <si>
-    <t>04/02/2026</t>
-  </si>
-  <si>
-    <t>15/04/2026</t>
-  </si>
-  <si>
-    <t>37461</t>
-  </si>
-  <si>
-    <t>Altona || Adiantamento de Clientes do Exterior - Relatório de Variação Cambial - (Reunião)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solicito a criação de uma rotina e posteriormente de um relatório que faça a demonstração da variação cambial dos adiantamentos de clientes do exterior. Para isso é preciso: 1) Criar um campo para cadastrar a moeda e sua respectiva cotação. Essa cotação será alimentada manualmente. Exemplo: Dólar – </t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>37475</t>
-  </si>
-  <si>
-    <t>BOTÃO ALTERAÇÃO DE TEMPO SIMULTÂNEA</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor criar um botão na tela UCPP11 que possibilite incluir o tempo em mais de um setor selecionado. OBS: Ideia alinhada com o Sr. Sandro Schram. Qualquer dúvida, estou à disposição. Obrigada, At.te</t>
-  </si>
-  <si>
-    <t>Karolina Moreira da Silva</t>
-  </si>
-  <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
-    <t>36232</t>
-  </si>
-  <si>
-    <t>Report técnico - Acompanhamento</t>
-  </si>
-  <si>
-    <t>33631</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - Custos</t>
-  </si>
-  <si>
-    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
-  </si>
-  <si>
-    <t>Marcelo Americo</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>20/08/2025</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>30069</t>
-  </si>
-  <si>
-    <t>Controle de Importação - integração financeira</t>
-  </si>
-  <si>
-    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>11/02/2025</t>
-  </si>
-  <si>
-    <t>36219</t>
-  </si>
-  <si>
-    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
-  </si>
-  <si>
-    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
-    <t>Como teremos 3 modelagens as op’s poderão ter quantidades diferentes nas modelagens, validar com o pessoal do APS essa interligação.</t>
-  </si>
-  <si>
-    <t>36335</t>
-  </si>
-  <si>
-    <t>Ajuste em gráficos no B.I</t>
-  </si>
-  <si>
-    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>36541</t>
-  </si>
-  <si>
-    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
-  </si>
-  <si>
-    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
-  </si>
-  <si>
-    <t>Alini Ferreira Ganda</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>36728</t>
-  </si>
-  <si>
-    <t>Aplicação QlikSense - Custeio FTF</t>
-  </si>
-  <si>
-    <t>Bom dia Felipe. Desenvolver um QVD para aplicação que possamos consultar custo FTF, semelhante informações do relatório FTF anexo.</t>
-  </si>
-  <si>
-    <t>22/04/2026</t>
-  </si>
-  <si>
-    <t>37498</t>
-  </si>
-  <si>
-    <t>Alteração sistema registro USE-ULE Windows</t>
-  </si>
-  <si>
-    <t>Bom dia, Necessitamos que seja alterado a forma que os registros da moldagem são exibidos ao clicar no botão "Imprime Registro". Atualmente ao clicar no botão recebemos as informações com as respostas dos setores de preparação, moldagem, fechamento e desmoldagem, deixando de fora o setor da macharia</t>
-  </si>
-  <si>
-    <t>João Eduardo Zarth</t>
-  </si>
-  <si>
-    <t>26/03/2026</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>37288</t>
-  </si>
-  <si>
-    <t>melhoria no sistema de inventário das embalagens</t>
-  </si>
-  <si>
-    <t>Bom dia! Com o aval do Rafael, solicito uma melhoria no sistema de inventário das embalagens (caixas Magayver). Atualmente, o sistema considera apenas as embalagens contadas fisicamente. Porém, existe a possibilidade de haver saldo no sistema mesmo quando a embalagem não existe fisicamente. Diante d</t>
-  </si>
-  <si>
-    <t>36430</t>
-  </si>
-  <si>
-    <t>Indicadores de Setup - IROG Usinagem</t>
-  </si>
-  <si>
-    <t>________________________________ De: Pedro Henrique Poburko Enviado: terça-feira, 3 de fevereiro de 2026 14:06 Para: Suporte Altona Assunto: RE: Resolvido: Indicadores de Setup - IROG Usinagem Felipe, bom dia. Precisamos que o tempo de entrega do indicador abaixo seja removido. Consegue alterar, por</t>
-  </si>
-  <si>
-    <t>Pedro Henrique Poburko</t>
-  </si>
-  <si>
-    <t>03/02/2026</t>
-  </si>
-  <si>
-    <t>36218</t>
-  </si>
-  <si>
-    <t>Melhoria Aplicação QlikSense - Custeio Valor</t>
-  </si>
-  <si>
-    <t>Felipe bom dia! Importar para aplicação de Custeio planilhas Excel com a base de ajustes gerenciais, concatenando com o QVD de extração de dados diretamente do Sistema de Custeio.</t>
-  </si>
-  <si>
-    <t>37514</t>
-  </si>
-  <si>
-    <t>Melhoria cadastro de matérias</t>
-  </si>
-  <si>
-    <t>Boa tarde, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1. Gostaria de solicitar a implementação de um campo no sistema que permita a geração de uma planilha em Excel antes da aprovação do cadastro. Att,</t>
-  </si>
-  <si>
-    <t>Vanessa Knoth</t>
-  </si>
-  <si>
-    <t>36206</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web (copy)</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>37526</t>
-  </si>
-  <si>
-    <t>PDI - Relatório de apontamentos</t>
-  </si>
-  <si>
-    <t>Verificar a situação apresentada pelo usuário Gerson Mendonça: Atenciosamente,</t>
-  </si>
-  <si>
     <t>27/03/2026</t>
   </si>
   <si>
@@ -867,12 +855,6 @@
     <t>Sequencial number Clientes</t>
   </si>
   <si>
-    <t>Boa tarde, Conforme conversado com o Sr. Flavio, precisamos criar uma regrar referente aos clientes da Altona que necessitam de um serial number fora a parte, que anda em paralelo da sequência da peça, um exemplo é a Solar Turbines. Esse "lot number" é criado no momento da programação da sequência q</t>
-  </si>
-  <si>
-    <t>Jackson Souza</t>
-  </si>
-  <si>
     <t>36648</t>
   </si>
   <si>
@@ -900,6 +882,9 @@
     <t>23/03/2026</t>
   </si>
   <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
     <t>29853</t>
   </si>
   <si>
@@ -1050,12 +1035,6 @@
     <t>IDENTIFICADOR ESPECIAL - LOT NUMBER</t>
   </si>
   <si>
-    <t>Bom dia, Favor criar um sistema de cadastro de identificador especial similar ao já existente da tela de cadastro TCPP45ID e consulta WCPP221J: Favor criar uma nova opção na tela TCPP45ID denominada "Possui controle ID especial?", sendo que se respondida como "SIM" permita o preenchimento dos seguin</t>
-  </si>
-  <si>
-    <t>14/01/2026</t>
-  </si>
-  <si>
     <t>36355</t>
   </si>
   <si>
@@ -1125,6 +1104,9 @@
     <t>20/03/2026</t>
   </si>
   <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
     <t>33549</t>
   </si>
   <si>
@@ -1200,9 +1182,6 @@
     <t>Alteração de registro de pintura</t>
   </si>
   <si>
-    <t>Sistema de registro de pintura: Teria como o Log aparecer de uma forma parecida com essa descrição? ( Cadastro de quem alterou), (Descrição do que foi alterado Ex. Alterado medição da camada Top Coat com tolerância: Min.: ........., Max.: .........., Medição anterior: ............, Alterado para: ..</t>
-  </si>
-  <si>
     <t>37190</t>
   </si>
   <si>
@@ -1248,7 +1227,7 @@
     <t>16/03/2026</t>
   </si>
   <si>
-    <t>17/05/2026</t>
+    <t>12/05/2026</t>
   </si>
   <si>
     <t>35448</t>
@@ -1989,13 +1968,13 @@
         <v>37</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>27</v>
@@ -2003,37 +1982,37 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>45</v>
@@ -2077,7 +2056,7 @@
         <v>51</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -2121,7 +2100,7 @@
         <v>57</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -2165,13 +2144,13 @@
         <v>63</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>64</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -2209,13 +2188,13 @@
         <v>69</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>70</v>
@@ -2253,7 +2232,7 @@
         <v>75</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -2297,7 +2276,7 @@
         <v>80</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -2341,13 +2320,13 @@
         <v>86</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>27</v>
@@ -2385,13 +2364,13 @@
         <v>90</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>91</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>27</v>
@@ -2429,7 +2408,7 @@
         <v>96</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -2567,7 +2546,7 @@
         <v>91</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>70</v>
@@ -2825,7 +2804,7 @@
         <v>142</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>45</v>
@@ -2848,25 +2827,25 @@
         <v>16</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>144</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>147</v>
+        <v>29</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>29</v>
@@ -2875,10 +2854,10 @@
         <v>91</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -2895,10 +2874,10 @@
         <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -2919,7 +2898,7 @@
         <v>25</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>29</v>
@@ -2927,7 +2906,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2939,10 +2918,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -2954,7 +2933,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>29</v>
@@ -2971,7 +2950,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2983,10 +2962,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
@@ -2998,10 +2977,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -3027,7 +3006,7 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
@@ -3045,13 +3024,13 @@
         <v>90</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>91</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>27</v>
@@ -3059,7 +3038,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -3071,25 +3050,25 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -3103,7 +3082,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -3115,10 +3094,10 @@
         <v>29</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
@@ -3147,7 +3126,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -3159,16 +3138,16 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>22</v>
@@ -3177,7 +3156,7 @@
         <v>134</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>91</v>
@@ -3203,7 +3182,7 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>89</v>
@@ -3221,13 +3200,13 @@
         <v>90</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>91</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>27</v>
@@ -3235,7 +3214,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -3247,25 +3226,25 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -3279,7 +3258,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -3291,25 +3270,25 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>91</v>
@@ -3323,7 +3302,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -3335,25 +3314,25 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -3367,7 +3346,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -3376,72 +3355,72 @@
         <v>16</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>29</v>
+        <v>185</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H37" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I37" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="J37" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="J37" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="K37" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>103</v>
@@ -3450,12 +3429,12 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -3467,22 +3446,22 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H38" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>29</v>
@@ -3491,7 +3470,7 @@
         <v>45</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>70</v>
@@ -3499,34 +3478,34 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>201</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>29</v>
@@ -3555,7 +3534,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>67</v>
@@ -3573,13 +3552,13 @@
         <v>69</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>91</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>70</v>
@@ -3587,22 +3566,22 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3614,7 +3593,7 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>29</v>
@@ -3631,7 +3610,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3640,42 +3619,42 @@
         <v>16</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>212</v>
+        <v>29</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>213</v>
+        <v>29</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3687,25 +3666,25 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>218</v>
+        <v>24</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3719,7 +3698,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3731,25 +3710,25 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3763,7 +3742,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3775,10 +3754,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>31</v>
@@ -3787,10 +3766,10 @@
         <v>50</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>29</v>
@@ -3807,7 +3786,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3819,10 +3798,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>31</v>
@@ -3851,7 +3830,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3863,25 +3842,25 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3895,7 +3874,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3907,25 +3886,25 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>218</v>
+        <v>24</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3939,7 +3918,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3951,25 +3930,25 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3983,28 +3962,28 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>22</v>
@@ -4027,7 +4006,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -4039,25 +4018,25 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>91</v>
@@ -4071,7 +4050,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -4083,25 +4062,25 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>45</v>
@@ -4127,7 +4106,7 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>84</v>
@@ -4145,13 +4124,13 @@
         <v>86</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>27</v>
@@ -4159,7 +4138,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -4171,22 +4150,22 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>29</v>
@@ -4203,19 +4182,19 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>29</v>
@@ -4224,13 +4203,13 @@
         <v>31</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>29</v>
@@ -4242,48 +4221,48 @@
         <v>32</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>27</v>
@@ -4291,7 +4270,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -4303,10 +4282,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>31</v>
@@ -4318,10 +4297,10 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -4335,7 +4314,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -4347,28 +4326,28 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>26</v>
@@ -4379,19 +4358,19 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>29</v>
@@ -4400,13 +4379,13 @@
         <v>31</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>29</v>
@@ -4418,12 +4397,12 @@
         <v>32</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -4435,22 +4414,22 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>24</v>
@@ -4467,7 +4446,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -4476,25 +4455,25 @@
         <v>16</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>285</v>
+        <v>29</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>29</v>
@@ -4503,15 +4482,15 @@
         <v>45</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -4523,31 +4502,31 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>70</v>
@@ -4555,7 +4534,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4567,10 +4546,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>31</v>
@@ -4582,10 +4561,10 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>29</v>
+        <v>289</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>25</v>
@@ -4599,7 +4578,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4611,25 +4590,25 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>45</v>
@@ -4643,28 +4622,28 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>22</v>
@@ -4673,13 +4652,13 @@
         <v>86</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>27</v>
@@ -4687,7 +4666,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4696,16 +4675,16 @@
         <v>16</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>133</v>
@@ -4714,10 +4693,10 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4731,19 +4710,19 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>29</v>
@@ -4752,13 +4731,13 @@
         <v>31</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>29</v>
@@ -4770,12 +4749,12 @@
         <v>32</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4787,22 +4766,22 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>29</v>
@@ -4819,7 +4798,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4831,25 +4810,25 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>45</v>
@@ -4863,7 +4842,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4875,25 +4854,25 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>25</v>
@@ -4907,7 +4886,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4919,22 +4898,22 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>29</v>
@@ -4946,12 +4925,12 @@
         <v>32</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4960,25 +4939,25 @@
         <v>98</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>24</v>
@@ -4995,7 +4974,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -5007,22 +4986,22 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>29</v>
@@ -5039,7 +5018,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -5051,16 +5030,16 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>22</v>
@@ -5072,7 +5051,7 @@
         <v>29</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>26</v>
@@ -5083,22 +5062,22 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>31</v>
@@ -5127,7 +5106,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -5139,25 +5118,25 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>25</v>
@@ -5171,7 +5150,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -5180,25 +5159,25 @@
         <v>16</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>346</v>
+        <v>29</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>29</v>
@@ -5207,15 +5186,15 @@
         <v>103</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -5227,25 +5206,25 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>25</v>
@@ -5259,7 +5238,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -5271,22 +5250,22 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>29</v>
@@ -5303,7 +5282,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -5312,28 +5291,28 @@
         <v>98</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>25</v>
@@ -5347,7 +5326,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -5356,28 +5335,28 @@
         <v>16</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>25</v>
@@ -5391,7 +5370,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -5403,25 +5382,25 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>29</v>
+        <v>363</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>64</v>
@@ -5435,7 +5414,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -5447,39 +5426,39 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -5491,25 +5470,25 @@
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>25</v>
@@ -5523,7 +5502,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -5535,22 +5514,22 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>29</v>
@@ -5567,7 +5546,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5579,25 +5558,25 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>25</v>
@@ -5611,37 +5590,37 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>64</v>
@@ -5655,7 +5634,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5667,25 +5646,25 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>25</v>
@@ -5699,7 +5678,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5708,25 +5687,25 @@
         <v>16</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>147</v>
+        <v>29</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>29</v>
@@ -5735,15 +5714,15 @@
         <v>91</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5755,16 +5734,16 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>22</v>
@@ -5779,7 +5758,7 @@
         <v>103</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>27</v>
@@ -5787,7 +5766,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5799,25 +5778,25 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>355</v>
+        <v>213</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>25</v>
@@ -5826,7 +5805,7 @@
         <v>32</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
@@ -5837,13 +5816,13 @@
         <v>15</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>107</v>
@@ -5875,19 +5854,19 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>29</v>
@@ -5896,13 +5875,13 @@
         <v>31</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>29</v>
@@ -5914,12 +5893,12 @@
         <v>32</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5931,10 +5910,10 @@
         <v>17</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
@@ -5946,10 +5925,10 @@
         <v>22</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>25</v>
@@ -5963,7 +5942,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5975,10 +5954,10 @@
         <v>29</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>31</v>
@@ -6007,7 +5986,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -6016,13 +5995,13 @@
         <v>16</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>31</v>
@@ -6037,13 +6016,13 @@
         <v>114</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>91</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>70</v>
@@ -6051,7 +6030,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -6063,10 +6042,10 @@
         <v>29</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>31</v>
@@ -6095,7 +6074,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -6107,10 +6086,10 @@
         <v>29</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>31</v>
@@ -6139,7 +6118,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -6151,10 +6130,10 @@
         <v>17</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>31</v>
@@ -6166,10 +6145,10 @@
         <v>22</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>25</v>
@@ -6178,12 +6157,12 @@
         <v>46</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -6195,10 +6174,10 @@
         <v>17</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>31</v>
@@ -6210,10 +6189,10 @@
         <v>22</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>25</v>
@@ -6239,10 +6218,10 @@
         <v>29</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>31</v>
@@ -6263,7 +6242,7 @@
         <v>25</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>29</v>
@@ -6283,10 +6262,10 @@
         <v>29</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>31</v>
@@ -6307,7 +6286,7 @@
         <v>25</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N102" s="2" t="s">
         <v>29</v>
@@ -6315,7 +6294,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>15</v>
@@ -6327,57 +6306,57 @@
         <v>17</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>29</v>
@@ -6414,23 +6393,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B2" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="D2" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="E2" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6438,16 +6417,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6455,7 +6434,7 @@
         <v>103</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>0.009708737864077669</v>
       </c>
       <c r="G5" s="4">
         <v>19.15</v>
@@ -6466,7 +6445,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6487,7 +6466,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6518,12 +6497,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B2">
         <v>103</v>
@@ -6531,7 +6510,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0</v>
+        <v>0.009708737864077669</v>
       </c>
       <c r="B5" s="7"/>
     </row>
@@ -6547,25 +6526,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6582,16 +6561,16 @@
         <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
@@ -6603,7 +6582,7 @@
         <v>46</v>
       </c>
       <c r="Q10">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -6620,10 +6599,10 @@
         <v>41</v>
       </c>
       <c r="J11" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="K11">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M11" t="s">
         <v>91</v>
@@ -6632,15 +6611,15 @@
         <v>23</v>
       </c>
       <c r="P11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -6652,7 +6631,7 @@
         <v>60</v>
       </c>
       <c r="M12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -6661,7 +6640,7 @@
         <v>26</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -6672,7 +6651,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -6687,18 +6666,18 @@
         <v>32</v>
       </c>
       <c r="Q13">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6713,12 +6692,12 @@
         <v>58</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -6732,7 +6711,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6740,7 +6719,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6748,7 +6727,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -6759,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6767,35 +6746,35 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
@@ -6804,7 +6783,7 @@
         <v>458</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6815,52 +6794,52 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>66</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>194</v>
+        <v>65</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6871,7 +6850,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>106</v>
@@ -6885,24 +6864,24 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2026-11.xlsx
+++ b/utils/monday_sprint_sprint_2026-11.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="435">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -63,51 +63,54 @@
     <t>37302</t>
   </si>
   <si>
+    <t>Usinagem</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Alteração do apontamento de solda</t>
+  </si>
+  <si>
+    <t>Se faz necessário alterar o registro de apontamento de solda para que seja possível apontar vareta por 0,25 / 0,50 / 0,75 / 1 .</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Lucas Sebold Movidesk</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>11571420448</t>
+  </si>
+  <si>
     <t>Setor não informado</t>
   </si>
   <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Alteração do apontamento de solda</t>
-  </si>
-  <si>
-    <t>Se faz necessário alterar o registro de apontamento de solda para que seja possível apontar vareta por 0,25 / 0,50 / 0,75 / 1 .</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Lucas Sebold Movidesk</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>22/04/2026</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>35602</t>
-  </si>
-  <si>
     <t>Categoria não informada</t>
   </si>
   <si>
@@ -126,1117 +129,1177 @@
     <t>23/03/2026</t>
   </si>
   <si>
+    <t>16/04/2026</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>37168</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Botão de pendente!</t>
+  </si>
+  <si>
+    <t>Boa tarde, Inserir um botão de pendente caso não tenhamos o material solicitado, e que fique em cor laranja a linha e vai pra outra aba de pendencias, assim que tivermos o material entregamos. At.te</t>
+  </si>
+  <si>
+    <t>Johnny José Rocha</t>
+  </si>
+  <si>
+    <t>37095</t>
+  </si>
+  <si>
+    <t>Logistica</t>
+  </si>
+  <si>
+    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
+  </si>
+  <si>
+    <t>Rodrigo Santos Rocha</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>36201</t>
+  </si>
+  <si>
+    <t>Engenharia</t>
+  </si>
+  <si>
+    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>37573</t>
+  </si>
+  <si>
+    <t>Mapeamento digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde Srs, Notamos ainda alguns pontos que seria interessante se possível alterar para termos mais agilidades ao finalizar os mapeamentos em caso das peças terem uma quantidade grande de cavidades. · Temos a questão que se for uma quantidade de foto acima de 30 fotos, para ti visualizar tem que </t>
+  </si>
+  <si>
+    <t>Danilo da Silva Pereira</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>37230</t>
+  </si>
+  <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
+    <t>Melhoria SMI - Solicitação da supervisão</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
+  </si>
+  <si>
+    <t>Enzo Luiz Okabe Auad</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy) (copy)</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
+  </si>
+  <si>
+    <t>37313</t>
+  </si>
+  <si>
+    <t>Adicionar Coluna de Frete</t>
+  </si>
+  <si>
+    <t>Bom dia, tudo bem? Poderiam por gentileza inserir uma coluna de valor de frete da mesma maneira como é atualmente na oferta sem lista de preço, para que puxe corretamente na CPC de lista de preço (em amarelo abaixo)? Obrigada!</t>
+  </si>
+  <si>
+    <t>Luana Brito Ribeiro</t>
+  </si>
+  <si>
+    <t>34403</t>
+  </si>
+  <si>
+    <t>Fundição</t>
+  </si>
+  <si>
+    <t>Adicionar opção de trocar observação - Paradas sem peça</t>
+  </si>
+  <si>
+    <t>Boa tarde, seria muito bom se desse para trocar a observação na hora de apontar as paradas: Já que por exemplo no setor 1504 - Corte e Escarfa a gente aponta a Linha 1 e a Linha 2 e colocamos na observação quando apontamos produção, mas as paradas não dá, então na hora de extrair não tem como difere</t>
+  </si>
+  <si>
+    <t>Maria Eduarda Santos</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>37197</t>
+  </si>
+  <si>
+    <t>Melhorias sistema de Tratamento Térmico - Sequencia Não Movimentada</t>
+  </si>
+  <si>
+    <t>Boa tarde, Pensando em facilitar a transição do papel para o sistema de tratamento térmico, observamos que precisamos de algumas melhorias para deixar de usar o papel. * Criar o Checklist dos 3 processos que precisam ser preenchidos de acordo as etapas de montagem de cargas(Preparação da carga, Carr</t>
+  </si>
+  <si>
+    <t>Eduardo Basso Pinto</t>
+  </si>
+  <si>
+    <t>37129</t>
+  </si>
+  <si>
+    <t>Esses relatórios também devem estar disponíveis na aba de relatórios para extração em excel a qualquer momento (copy)</t>
+  </si>
+  <si>
+    <t>Bom dia, Chamado Prioritário para correção de não conformidade identificada durante auditoria terceirizada não oficial da ISO 9001. Recentemente foi feita uma alteração no sistema na qual as ordens preventivas ao checar na caixa ilustrada abaixo sejam abertas como uma SS (solicitação de serviço) com</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>37001</t>
+  </si>
+  <si>
+    <t>Mecânica</t>
+  </si>
+  <si>
+    <t>Comparativo de horas paradas entre SMI e MES</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito um chamado para fazer um comparativo de horas paradas entre SMI e MESS, disponibilizando um dashboard na aplicação de controle de manutenção do QlikSense</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>11465676193</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Erro Planilhão - Itens conjuntos</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>11678123897</t>
+  </si>
+  <si>
+    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada (copy) (copy)</t>
+  </si>
+  <si>
+    <t>12/04/2026</t>
+  </si>
+  <si>
+    <t>11678122173</t>
+  </si>
+  <si>
+    <t>Multiplos de Caixa de ferro</t>
+  </si>
+  <si>
+    <t>05/04/2026</t>
+  </si>
+  <si>
+    <t>33965</t>
+  </si>
+  <si>
+    <t>Apontamento de moldes Carrossel - Testes</t>
+  </si>
+  <si>
+    <t>Boa tarde, Necessário criar no apontamento para carrossel, identificando a sequência e se são as partes superiores e Inferiores. Att.</t>
+  </si>
+  <si>
+    <t>Matheus Rodrigues de Almeida</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>36482</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Estorno para inventário</t>
+  </si>
+  <si>
+    <t>Identificamos a necessidade de criar uma nova funcionalidade no sistema de inventário, válida para todas as modalidades: a opção de estornar inventário. Atualmente, quando ocorre algum erro, precisamos estornar item por item, o que demanda um tempo significativo e impacta diretamente na agilidade da</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>35380</t>
+  </si>
+  <si>
+    <t>inclusão de saldo EPI higienizado</t>
+  </si>
+  <si>
+    <t>Boa tarde! Solicito a inclusão de uma nova funcionalidade no WMS do Almoxarifado, denominada "Saldo Higienizado". Essa funcionalidade já existe no ERP, conforme demonstrarei através de print, precisamos que seja disponibilizada também no WMS, para que possamos incluir o saldo de EPI's higienizados p</t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>37552</t>
+  </si>
+  <si>
+    <t>Requisições BINAAR - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia. Solicitação de implementação de sistema WMS para requisição de itens na manutenção de equipamentos pneumáticos. Utilização de coletor para leitura dos itens utilizados em cada equipamentos consertado. Importante ressaltar que existem itens utilizados que não são fornecidos pela BINAAR, como</t>
+  </si>
+  <si>
+    <t>Bruno da Silva</t>
+  </si>
+  <si>
+    <t>11678210428</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
+  </si>
+  <si>
+    <t>37082</t>
+  </si>
+  <si>
+    <t>Ajuste de sistema</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor permitir que o setor 7273 seja eliminado de várias sequências ao mesmo tempo pelos seguintes usuários: 142830 / 131580 / 145566</t>
+  </si>
+  <si>
+    <t>Paula Rosa M. Grando</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>36722</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>Bloco K - Integração dados Altona / Benner.</t>
+  </si>
+  <si>
+    <t>Prezado, bom dia. Situação: Atualmente a integração dos dados Altona / Benner, para integrar o bloco K, precisa da intervenção de uma pessoa para disparar a rotina. Necessidade: Automatizar este processo. Ação: 1. Implementar status indicando que o dado está pronto para ser enviado para Benner. 2. A</t>
+  </si>
+  <si>
+    <t>Alexandre Longo</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>11469902776</t>
+  </si>
+  <si>
+    <t>Coleta e identificação de sequencia</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>11447450076</t>
+  </si>
+  <si>
+    <t>NOVOS INDICADORES BI - Reunião</t>
+  </si>
+  <si>
+    <t>37105</t>
+  </si>
+  <si>
+    <t>Melhoria na tela de baixa de ordens preventivas e corretivas</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos implementar uma melhoria no sistema, a ideia é deixarmos um botão disponível na tela de baixa de ordens tanto preventivas quanto corretivas. Hoje estamos utilizando a opção de anexos do equipamento: A Ideia é que nas telas de baixa de ordens (são as telas que os mantenedores ma</t>
+  </si>
+  <si>
+    <t>Implementar Alerta de Solicitações de serviço com status de aguardando programação</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>36968</t>
+  </si>
+  <si>
+    <t>ADICIONAR MOTIVO DE PARADA - C. PARADA - 232 / DESCRIÇÃO - TROCA DE GÁS</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito adicionar; C. Parada Descrição 232 TROCA DE GÁS. MOTIVO: O soldador de produção, leva um tempo considerável para fazer o Setup e precisamos estratificar este tempo para avaliar a eficiência. At.te,</t>
+  </si>
+  <si>
+    <t>Juliano Carriel</t>
+  </si>
+  <si>
+    <t>11664026694</t>
+  </si>
+  <si>
+    <t>Layout ofertas exportação</t>
+  </si>
+  <si>
+    <t>37563</t>
+  </si>
+  <si>
+    <t>Corridas Fora de Liga</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos que esse relatório gere a opção de excel. Com as informações de Forno, Corrida, Liga, Faixa Mínima, Faixa Máxima e mensurado Local onde pode ser adicionado o botão, após colocar as informações de ano e forno abre essa tela, e nessa tela incluir um botão para gerar um excel de t</t>
+  </si>
+  <si>
+    <t>Espectrometria</t>
+  </si>
+  <si>
+    <t>Implementar Alerta Ordens de serviços com data de programação (já programadas) e não foram executadas</t>
+  </si>
+  <si>
+    <t>36467</t>
+  </si>
+  <si>
+    <t>Sitema retrabalho ajustagem com erro</t>
+  </si>
+  <si>
+    <t>Boa tarde! Enviando para o Email correto. Gentileza considerar o e-mail abaixo. Atenciosamente, De: Fernanda da Costa Rodrigues Enviada em: quarta-feira, 4 de fevereiro de 2026 14:25 Para: 'Suporte Altona' Cc: Edson João Hammermeister ; Lucas José Sebold Assunto: RES: Resolvido: Sitema retrabalho aj</t>
+  </si>
+  <si>
+    <t>Fernanda da Costa Rodrigues</t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>37461</t>
+  </si>
+  <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
+    <t>Altona || Adiantamento de Clientes do Exterior - Relatório de Variação Cambial - (Reunião)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solicito a criação de uma rotina e posteriormente de um relatório que faça a demonstração da variação cambial dos adiantamentos de clientes do exterior. Para isso é preciso: 1) Criar um campo para cadastrar a moeda e sua respectiva cotação. Essa cotação será alimentada manualmente. Exemplo: Dólar – </t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
+  </si>
+  <si>
+    <t>37475</t>
+  </si>
+  <si>
+    <t>Planejamento Técnico</t>
+  </si>
+  <si>
+    <t>BOTÃO ALTERAÇÃO DE TEMPO SIMULTÂNEA</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor criar um botão na tela UCPP11 que possibilite incluir o tempo em mais de um setor selecionado. OBS: Ideia alinhada com o Sr. Sandro Schram. Qualquer dúvida, estou à disposição. Obrigada, At.te</t>
+  </si>
+  <si>
+    <t>Karolina Moreira da Silva</t>
+  </si>
+  <si>
+    <t>36232</t>
+  </si>
+  <si>
+    <t>Report técnico - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
+    <t>33631</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - Custos</t>
+  </si>
+  <si>
+    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
+  </si>
+  <si>
+    <t>Marcelo Americo</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>30069</t>
+  </si>
+  <si>
+    <t>Controle de Importação - integração financeira</t>
+  </si>
+  <si>
+    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>15/04/2026</t>
+  </si>
+  <si>
+    <t>36219</t>
+  </si>
+  <si>
+    <t>Controladoria</t>
+  </si>
+  <si>
+    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
+  </si>
+  <si>
+    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>Como teremos 3 modelagens as op’s poderão ter quantidades diferentes nas modelagens, validar com o pessoal do APS essa interligação.</t>
+  </si>
+  <si>
+    <t>36335</t>
+  </si>
+  <si>
+    <t>Ajuste em gráficos no B.I</t>
+  </si>
+  <si>
+    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
+  </si>
+  <si>
+    <t>36541</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
+  </si>
+  <si>
+    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
+  </si>
+  <si>
+    <t>Alini Ferreira Ganda</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>36728</t>
+  </si>
+  <si>
+    <t>Aplicação QlikSense - Custeio FTF</t>
+  </si>
+  <si>
+    <t>Bom dia Felipe. Desenvolver um QVD para aplicação que possamos consultar custo FTF, semelhante informações do relatório FTF anexo.</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>37498</t>
+  </si>
+  <si>
+    <t>Alteração sistema registro USE-ULE Windows</t>
+  </si>
+  <si>
+    <t>Bom dia, Necessitamos que seja alterado a forma que os registros da moldagem são exibidos ao clicar no botão "Imprime Registro". Atualmente ao clicar no botão recebemos as informações com as respostas dos setores de preparação, moldagem, fechamento e desmoldagem, deixando de fora o setor da macharia</t>
+  </si>
+  <si>
+    <t>João Eduardo Zarth</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>37288</t>
+  </si>
+  <si>
+    <t>melhoria no sistema de inventário das embalagens</t>
+  </si>
+  <si>
+    <t>Bom dia! Com o aval do Rafael, solicito uma melhoria no sistema de inventário das embalagens (caixas Magayver). Atualmente, o sistema considera apenas as embalagens contadas fisicamente. Porém, existe a possibilidade de haver saldo no sistema mesmo quando a embalagem não existe fisicamente. Diante d</t>
+  </si>
+  <si>
+    <t>36430</t>
+  </si>
+  <si>
+    <t>Indicadores de Setup - IROG Usinagem</t>
+  </si>
+  <si>
+    <t>________________________________ De: Pedro Henrique Poburko Enviado: terça-feira, 3 de fevereiro de 2026 14:06 Para: Suporte Altona Assunto: RE: Resolvido: Indicadores de Setup - IROG Usinagem Felipe, bom dia. Precisamos que o tempo de entrega do indicador abaixo seja removido. Consegue alterar, por</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Poburko</t>
+  </si>
+  <si>
+    <t>36218</t>
+  </si>
+  <si>
+    <t>Melhoria Aplicação QlikSense - Custeio Valor</t>
+  </si>
+  <si>
+    <t>Felipe bom dia! Importar para aplicação de Custeio planilhas Excel com a base de ajustes gerenciais, concatenando com o QVD de extração de dados diretamente do Sistema de Custeio.</t>
+  </si>
+  <si>
+    <t>37514</t>
+  </si>
+  <si>
+    <t>Melhoria cadastro de matérias</t>
+  </si>
+  <si>
+    <t>Boa tarde, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1. Gostaria de solicitar a implementação de um campo no sistema que permita a geração de uma planilha em Excel antes da aprovação do cadastro. Att,</t>
+  </si>
+  <si>
+    <t>Vanessa Knoth</t>
+  </si>
+  <si>
+    <t>36206</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web (copy)</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>37526</t>
+  </si>
+  <si>
+    <t>PDI - Relatório de apontamentos</t>
+  </si>
+  <si>
+    <t>Verificar a situação apresentada pelo usuário Gerson Mendonça: Atenciosamente,</t>
+  </si>
+  <si>
+    <t>37499</t>
+  </si>
+  <si>
+    <t>Bom dia, Necessitamos que seja feita uma alteração no sistema de registro USE-ULE, precisamos que as imagens que ficam anexas as perguntas, quando exibidas pelo relatório do botão "Imprime Registro" sejam de um tamanho maior, que seja possível analisar de forma clara pelo computador. Sugerimos que s</t>
+  </si>
+  <si>
+    <t>Melhorias sistema de Tratamento Térmico - Checklist</t>
+  </si>
+  <si>
+    <t>36920</t>
+  </si>
+  <si>
+    <t>Link para vídeos</t>
+  </si>
+  <si>
+    <t>Bom dia, Estamos rodando o projeto de procedimentos por vídeos, necessitamos da criação de um link que possa ser acessado na aba documentos anexos dentro do sistema PCP, quando acessado o link, o colaborador assiste o vídeo que está no diretório, temos atualmente 10 vídeos para rodar o piloto. [Prec</t>
+  </si>
+  <si>
+    <t>Filipe Rosa</t>
+  </si>
+  <si>
+    <t>27/05/2026</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Tela apoio para forçar envio de dados.</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>37168</t>
-  </si>
-  <si>
-    <t>Logística</t>
-  </si>
-  <si>
-    <t>Botão de pendente!</t>
-  </si>
-  <si>
-    <t>Boa tarde, Inserir um botão de pendente caso não tenhamos o material solicitado, e que fique em cor laranja a linha e vai pra outra aba de pendencias, assim que tivermos o material entregamos. At.te</t>
-  </si>
-  <si>
-    <t>Johnny José Rocha</t>
-  </si>
-  <si>
-    <t>37095</t>
-  </si>
-  <si>
-    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
-  </si>
-  <si>
-    <t>Rodrigo Santos Rocha</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>36201</t>
-  </si>
-  <si>
-    <t>Engenharia</t>
-  </si>
-  <si>
-    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>06/04/2026</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>37573</t>
-  </si>
-  <si>
-    <t>Mapeamento digital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde Srs, Notamos ainda alguns pontos que seria interessante se possível alterar para termos mais agilidades ao finalizar os mapeamentos em caso das peças terem uma quantidade grande de cavidades. · Temos a questão que se for uma quantidade de foto acima de 30 fotos, para ti visualizar tem que </t>
-  </si>
-  <si>
-    <t>Danilo da Silva Pereira</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>37230</t>
-  </si>
-  <si>
-    <t>Melhoria SMI - Solicitação da supervisão</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
-  </si>
-  <si>
-    <t>Enzo Luiz Okabe Auad</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy) (copy)</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
-  </si>
-  <si>
-    <t>37313</t>
-  </si>
-  <si>
-    <t>Adicionar Coluna de Frete</t>
-  </si>
-  <si>
-    <t>Bom dia, tudo bem? Poderiam por gentileza inserir uma coluna de valor de frete da mesma maneira como é atualmente na oferta sem lista de preço, para que puxe corretamente na CPC de lista de preço (em amarelo abaixo)? Obrigada!</t>
-  </si>
-  <si>
-    <t>Luana Brito Ribeiro</t>
-  </si>
-  <si>
-    <t>34403</t>
-  </si>
-  <si>
-    <t>Adicionar opção de trocar observação - Paradas sem peça</t>
-  </si>
-  <si>
-    <t>Boa tarde, seria muito bom se desse para trocar a observação na hora de apontar as paradas: Já que por exemplo no setor 1504 - Corte e Escarfa a gente aponta a Linha 1 e a Linha 2 e colocamos na observação quando apontamos produção, mas as paradas não dá, então na hora de extrair não tem como difere</t>
-  </si>
-  <si>
-    <t>Maria Eduarda Santos</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>37197</t>
-  </si>
-  <si>
-    <t>Melhorias sistema de Tratamento Térmico - Sequencia Não Movimentada</t>
-  </si>
-  <si>
-    <t>Boa tarde, Pensando em facilitar a transição do papel para o sistema de tratamento térmico, observamos que precisamos de algumas melhorias para deixar de usar o papel. * Criar o Checklist dos 3 processos que precisam ser preenchidos de acordo as etapas de montagem de cargas(Preparação da carga, Carr</t>
-  </si>
-  <si>
-    <t>Eduardo Basso Pinto</t>
-  </si>
-  <si>
-    <t>37129</t>
-  </si>
-  <si>
-    <t>Esses relatórios também devem estar disponíveis na aba de relatórios para extração em excel a qualquer momento (copy)</t>
-  </si>
-  <si>
-    <t>Bom dia, Chamado Prioritário para correção de não conformidade identificada durante auditoria terceirizada não oficial da ISO 9001. Recentemente foi feita uma alteração no sistema na qual as ordens preventivas ao checar na caixa ilustrada abaixo sejam abertas como uma SS (solicitação de serviço) com</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>37001</t>
-  </si>
-  <si>
-    <t>Comparativo de horas paradas entre SMI e MES</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito um chamado para fazer um comparativo de horas paradas entre SMI e MESS, disponibilizando um dashboard na aplicação de controle de manutenção do QlikSense</t>
-  </si>
-  <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
-    <t>35727</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Erro Planilhão - Itens conjuntos</t>
-  </si>
-  <si>
-    <t>Boa tarde Pela primeira vez na UPR, teremos um item de fundido que atenderá a dois conjuntos diferentes. Atualmente, temos 13 peças do fundido em processo e 4 peças dos conjuntos em depósito. No entanto, o Planilhão está considerando apenas 1 peça em estoque, não reconhecendo as outras 3. É importan</t>
-  </si>
-  <si>
-    <t>Taynara Frare</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>32079</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada (copy) (copy)</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>36632</t>
-  </si>
-  <si>
-    <t>Multiplos de Caixa de ferro</t>
-  </si>
-  <si>
-    <t>33965</t>
-  </si>
-  <si>
-    <t>Fundição</t>
-  </si>
-  <si>
-    <t>Apontamento de moldes Carrossel - Testes</t>
-  </si>
-  <si>
-    <t>Boa tarde, Necessário criar no apontamento para carrossel, identificando a sequência e se são as partes superiores e Inferiores. Att.</t>
-  </si>
-  <si>
-    <t>Matheus Rodrigues de Almeida</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
-  </si>
-  <si>
-    <t>Fevereiro</t>
-  </si>
-  <si>
-    <t>36482</t>
-  </si>
-  <si>
-    <t>Almoxarifado</t>
-  </si>
-  <si>
-    <t>Estorno para inventário</t>
-  </si>
-  <si>
-    <t>Identificamos a necessidade de criar uma nova funcionalidade no sistema de inventário, válida para todas as modalidades: a opção de estornar inventário. Atualmente, quando ocorre algum erro, precisamos estornar item por item, o que demanda um tempo significativo e impacta diretamente na agilidade da</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>35380</t>
-  </si>
-  <si>
-    <t>inclusão de saldo EPI higienizado</t>
-  </si>
-  <si>
-    <t>Boa tarde! Solicito a inclusão de uma nova funcionalidade no WMS do Almoxarifado, denominada "Saldo Higienizado". Essa funcionalidade já existe no ERP, conforme demonstrarei através de print, precisamos que seja disponibilizada também no WMS, para que possamos incluir o saldo de EPI's higienizados p</t>
-  </si>
-  <si>
-    <t>28/11/2025</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>37552</t>
-  </si>
-  <si>
-    <t>Requisições BINAAR - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia. Solicitação de implementação de sistema WMS para requisição de itens na manutenção de equipamentos pneumáticos. Utilização de coletor para leitura dos itens utilizados em cada equipamentos consertado. Importante ressaltar que existem itens utilizados que não são fornecidos pela BINAAR, como</t>
-  </si>
-  <si>
-    <t>Bruno da Silva</t>
-  </si>
-  <si>
-    <t>23838</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
-  </si>
-  <si>
-    <t>37082</t>
-  </si>
-  <si>
-    <t>Ajuste de sistema</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor permitir que o setor 7273 seja eliminado de várias sequências ao mesmo tempo pelos seguintes usuários: 142830 / 131580 / 145566</t>
-  </si>
-  <si>
-    <t>Paula Rosa M. Grando</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>36722</t>
-  </si>
-  <si>
-    <t>Bloco K - Integração dados Altona / Benner.</t>
-  </si>
-  <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>Coleta e identificação de sequencia</t>
-  </si>
-  <si>
-    <t>37032</t>
-  </si>
-  <si>
-    <t>NOVOS INDICADORES BI - Reunião</t>
-  </si>
-  <si>
-    <t>37105</t>
-  </si>
-  <si>
-    <t>Melhoria na tela de baixa de ordens preventivas e corretivas</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos implementar uma melhoria no sistema, a ideia é deixarmos um botão disponível na tela de baixa de ordens tanto preventivas quanto corretivas. Hoje estamos utilizando a opção de anexos do equipamento: A Ideia é que nas telas de baixa de ordens (são as telas que os mantenedores ma</t>
-  </si>
-  <si>
-    <t>Implementar Alerta de Solicitações de serviço com status de aguardando programação</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>36968</t>
-  </si>
-  <si>
-    <t>ADICIONAR MOTIVO DE PARADA - C. PARADA - 232 / DESCRIÇÃO - TROCA DE GÁS</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito adicionar; C. Parada Descrição 232 TROCA DE GÁS. MOTIVO: O soldador de produção, leva um tempo considerável para fazer o Setup e precisamos estratificar este tempo para avaliar a eficiência. At.te,</t>
-  </si>
-  <si>
-    <t>Juliano Carriel</t>
-  </si>
-  <si>
-    <t>37530</t>
-  </si>
-  <si>
-    <t>Layout ofertas exportação</t>
-  </si>
-  <si>
-    <t>37563</t>
-  </si>
-  <si>
-    <t>Corridas Fora de Liga</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos que esse relatório gere a opção de excel. Com as informações de Forno, Corrida, Liga, Faixa Mínima, Faixa Máxima e mensurado Local onde pode ser adicionado o botão, após colocar as informações de ano e forno abre essa tela, e nessa tela incluir um botão para gerar um excel de t</t>
-  </si>
-  <si>
-    <t>Espectrometria</t>
-  </si>
-  <si>
-    <t>Implementar Alerta Ordens de serviços com data de programação (já programadas) e não foram executadas</t>
-  </si>
-  <si>
-    <t>36467</t>
-  </si>
-  <si>
-    <t>Sitema retrabalho ajustagem com erro</t>
-  </si>
-  <si>
-    <t>Boa tarde! Enviando para o Email correto. Gentileza considerar o e-mail abaixo. Atenciosamente, De: Fernanda da Costa Rodrigues Enviada em: quarta-feira, 4 de fevereiro de 2026 14:25 Para: 'Suporte Altona' Cc: Edson João Hammermeister ; Lucas José Sebold Assunto: RES: Resolvido: Sitema retrabalho aj</t>
-  </si>
-  <si>
-    <t>Fernanda da Costa Rodrigues</t>
-  </si>
-  <si>
-    <t>10/04/2026</t>
+    <t>Laura Herrmann Schmickler</t>
+  </si>
+  <si>
+    <t>37200</t>
+  </si>
+  <si>
+    <t>Apontamento Escarfa - Apresentacao e acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos da elaboração de um sistema web para o corte escarfa UPR. São duas linhas apontadas por um operador simultaneamente (linha 1 e linha 2), Pra facilitar visual do operador e dinâmica dividir as duas linhas na mesma tela, mas com todos os resultados separados. As sequencias devem se</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>37450</t>
+  </si>
+  <si>
+    <t>NOVOS CAMPOS DE DESENHO NA AC E NO CPP</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor criar campos de desenhos conforme abaixo nas telas do CPP tanto de consulta [WWCPP221] quanto de manutenção [TTCPP], e no PCP tela de alteração de dados da análise crítica [TANCR011] (no PCP não há necessidade dos campos "3D"): Tela original: Tela proposta: Alterações: "Usinagem F."</t>
+  </si>
+  <si>
+    <t>37361</t>
+  </si>
+  <si>
+    <t>Base Histórica da Data de Reconhecimento  de Receita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
+  </si>
+  <si>
+    <t>14/04/2026</t>
+  </si>
+  <si>
+    <t>Consulta log de registros.</t>
+  </si>
+  <si>
+    <t>36939</t>
+  </si>
+  <si>
+    <t>Incluir filtro "Select data range" - Usinagem IROG</t>
+  </si>
+  <si>
+    <t>Olá, Favor incluir o filtro "Select data range" na pasta principal da aplicação Usinagem IROG. Grato,</t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>11328519246</t>
+  </si>
+  <si>
+    <t>Sequencial number Clientes</t>
+  </si>
+  <si>
+    <t>18/04/2026</t>
+  </si>
+  <si>
+    <t>36648</t>
+  </si>
+  <si>
+    <t>Causa Raiz - BI retrabalho TT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Precisamos incluir no banco de dados do BI do retrabalho de Tratamento Térmico a causa raiz do retrabalho. Essa informação é crucial para usar o BI de forma integral, sem necessidade de suporte de excel paralelo. Atualmente no excel tenho o banco de dados dessa maneira: DIA MÊS MÊS EXTENSO </t>
+  </si>
+  <si>
+    <t>Gilberto José Rebelo Junior</t>
+  </si>
+  <si>
+    <t>37412</t>
+  </si>
+  <si>
+    <t>Registro de Preset - Reunião</t>
+  </si>
+  <si>
+    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>37182</t>
+  </si>
+  <si>
+    <t>Análise</t>
+  </si>
+  <si>
+    <t>AJUSTES - EXTRAÇÃO DE DADOS APONTAMENTO LINHA MESAS REDONDAS (copy)</t>
+  </si>
+  <si>
+    <t>Bom dia, No dia 10/03/2026 iniciamos o piloto de apontamento eletrônico na linha mesas redondas, feito a extração em Excel notamos alguns pontos que precisam ser ajustados. * Coluna Y plan 1 (percentual executado) - puxando informações incorretas comparando com o que está sendo apontado no tablet. *</t>
+  </si>
+  <si>
+    <t>36777</t>
+  </si>
+  <si>
+    <t>Dúvida</t>
+  </si>
+  <si>
+    <t>Data de admissão</t>
+  </si>
+  <si>
+    <t>Bom dia. Adicionar coluna "data de admiss?o" nas informa??es de requisi??o de materiais</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Atualizar campos: data, hora e prazo da proposta</t>
+  </si>
+  <si>
+    <t>36381</t>
+  </si>
+  <si>
+    <t>58B4660910 - 407LX - Movimentação sem fluxo</t>
+  </si>
+  <si>
+    <t>Bom dia, Senhores, Poderiam verificar o que ocorreu aqui? Mesma sequ?ncia unit?ria colocada em 02 etiquetas com 4 min de diferen?a. Foi dado entrada como "sequ?ncia sem fluxo". Estamos com pendencia de 01 pe?a e o sistema n?o mostra isso hoje. Registro de entrada 2 etiquetas diferentes com a mesma s</t>
+  </si>
+  <si>
+    <t>12/06/2026</t>
+  </si>
+  <si>
+    <t>32150</t>
+  </si>
+  <si>
+    <t>Inventario WMS - Registro de Ajuste de Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
+  </si>
+  <si>
+    <t>37485</t>
+  </si>
+  <si>
+    <t>opção de permissão</t>
+  </si>
+  <si>
+    <t>Boa tarde, Srs. Conforme falamos, a natureza do chamado tem como objetivo a solicitação de "permissão" para liderança da aciaria fazer movimentação as quais fogem do comum. Segue alguns exemplos abaixo: Onde fundimos 2 itens de ligas "Altona" diferentes 1304 e 1401. Onde não conseguimos baixar na co</t>
+  </si>
+  <si>
+    <t>Giancarlo Ibsch</t>
+  </si>
+  <si>
+    <t>11678146797</t>
+  </si>
+  <si>
+    <t>Melhoria WMS - Conferencia e Carregamento</t>
+  </si>
+  <si>
+    <t>36443</t>
+  </si>
+  <si>
+    <t>Problema</t>
+  </si>
+  <si>
+    <t>Falta dados - Aplicação Insertos Usinagem</t>
+  </si>
+  <si>
+    <t>Bom dia Felipe, Tudo certo? Favor verificar a aplicação de Insertos Usinagem, pois não está atualizando os dados desde o mês de outubro/2025. Uma aplicação que possui os dados da conta de insertos é a Consumo de Insumos e Materiais, porém não associa o modelo da peça e as máquinas da usinagem. Grato</t>
+  </si>
+  <si>
+    <t>32141</t>
+  </si>
+  <si>
+    <t>Cadastro de Embalagem no CPP</t>
+  </si>
+  <si>
+    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>37298</t>
+  </si>
+  <si>
+    <t>Melhoria | Custo de venda Orçamento Nacional</t>
+  </si>
+  <si>
+    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
+  </si>
+  <si>
+    <t>11678274013</t>
+  </si>
+  <si>
+    <t>ALTC - Verificar Retrabalho</t>
+  </si>
+  <si>
+    <t>37015</t>
+  </si>
+  <si>
+    <t>DIFA Interno e fretes - Ajuste de observação fiscal</t>
+  </si>
+  <si>
+    <t>Bom dia, Nas notas de DIFA interno e DIFA nos fretes precisa ser enviado os registros de observação fiscal e ajustes, conforme exemplo da NF 186758: O campo OBSERVACAO=@CODIGO(881) será o mesmo, o que vai mudar é o campo CODIGOAJUSTEBENEFICIO Nas notas de CFOP 1.556 e 1.551 o código de ajuste será S</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>11340072792</t>
+  </si>
+  <si>
+    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>36355</t>
+  </si>
+  <si>
+    <t>Alterar nome do filtro Ativo / Inativo para DESENV_ATIVOS e DESENV_INATIVOS</t>
+  </si>
+  <si>
+    <t>vide caminho para filtro no documento anexado.</t>
+  </si>
+  <si>
+    <t>11448172249</t>
+  </si>
+  <si>
+    <t>CRIAÇÃO DE B.I. PARA ACOMPANHAMENTO DE RESULTADOS DE ENSAIOS MECÂNICO - Reunião</t>
+  </si>
+  <si>
+    <t>23773</t>
+  </si>
+  <si>
+    <t>Registro de moldagem USE/ULE</t>
+  </si>
+  <si>
+    <t>Bom dia, Estamos tendo inconsistência nos registros de Moldagem USE/ULE, acontece às vezes do registro ser finalizado e a movimentação não ocorrer. Ocorre tanto na ULE como na USE. Exemplos abaixo: Duvidas entrar em contato. Att.</t>
+  </si>
+  <si>
+    <t>Darlan Pressi</t>
+  </si>
+  <si>
+    <t>36861</t>
+  </si>
+  <si>
+    <t>Aplicação de Solda</t>
+  </si>
+  <si>
+    <t>Bom dia, Gostaria de adicionar a informação do número do forno nesta tabela, ao lado da data de fusão. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Raiana Correa</t>
+  </si>
+  <si>
+    <t>37394</t>
+  </si>
+  <si>
+    <t>Rateio Jato Dirigido 1 e 2 - Fazer QG para atualizar operações na apon3 com base no estado da peça</t>
+  </si>
+  <si>
+    <t>Boa tarde, Hoje (20/03/26 ) foi criado as operações jato dirigido para cadastrarmos os tempos na CPP para rateio de tempo Qlik. Precisamos que esse rateio seja retroativo. No apontamento eletrônico o estado da peça era somente apontado para informação e não apontado sua real operação. Precisamos que</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>33549</t>
+  </si>
+  <si>
+    <t>Integração de sistema Logística x data book - Relatório x Registro End's</t>
+  </si>
+  <si>
+    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
+  </si>
+  <si>
+    <t>Rosivaldo Silva</t>
+  </si>
+  <si>
+    <t>35808</t>
+  </si>
+  <si>
+    <t>Unificação de dados das aplicações de "Apontamento solda" x "Retrabalho Rebarbação</t>
+  </si>
+  <si>
+    <t>Bom dia! Percebi que não houve saída para abertura de um chamado sobre esta demanda "Unificação de dados das aplicações de "Apontamento solda" x "Retrabalho Rebarbação - item solda"" solicitada durante reuniões de meados de agosto e setembro/2025 conforme meus registros aqui. Solicito por aqui, entã</t>
+  </si>
+  <si>
+    <t>Cadastro de Embalagem no CPP (APS)</t>
+  </si>
+  <si>
+    <t>36885</t>
+  </si>
+  <si>
+    <t>Qualidade</t>
+  </si>
+  <si>
+    <t>Incluir o numero da nova revisão no alerta enviado pelo Posto de Cópias eletrônico</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos que seja incluído no alerta de revisão, o número da nova revisão dos documentos e também alguns ajustes. Abaixo segue um de exemplo: Hoje: Olá, Matheus Gonçalves, Já consta disponível no Sistema de Posto de Cópias Eletrônico nova revisão do documento IT 658 PROCESSO DE RECRUTAM</t>
+  </si>
+  <si>
+    <t>Matheus Gonçalves</t>
+  </si>
+  <si>
+    <t>32133</t>
+  </si>
+  <si>
+    <t>Novo Recurso</t>
+  </si>
+  <si>
+    <t>Automatização planilha comercial - PARTE 1/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
+  </si>
+  <si>
+    <t>Jacson Schneider Movidesk</t>
+  </si>
+  <si>
+    <t>08/10/2025</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>34225</t>
+  </si>
+  <si>
+    <t>Correções Relatório Faturamento por Sequência - Acompanhamento (copy)</t>
+  </si>
+  <si>
+    <t>Sandro, bom dia! Solicito melhorias a seguir no Relatório Faturamento por Sequência. * Desconsiderar NF que não se tratam de venda (receita), por exemplo 210982/212675/213384/213385 (CFOP 5.949./6.949/7.949 - Remessa Conserto e Outros) NFe 213069 valor incorreto retornado no relatório.</t>
+  </si>
+  <si>
+    <t>11678201566</t>
+  </si>
+  <si>
+    <t>Alteração de registro de pintura</t>
+  </si>
+  <si>
+    <t>37190</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
+  </si>
+  <si>
+    <t>Guilherme Ferreira</t>
+  </si>
+  <si>
+    <t>11678232245</t>
+  </si>
+  <si>
+    <t>Criar KB Genexus especifica para Registro de pinturas</t>
+  </si>
+  <si>
+    <t>11678219914</t>
+  </si>
+  <si>
+    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES (copy)</t>
+  </si>
+  <si>
+    <t>Revisar os campos: data, hora e prazo da proposta</t>
+  </si>
+  <si>
+    <t>37256</t>
+  </si>
+  <si>
+    <t>Melhoria no sistema de ACR</t>
+  </si>
+  <si>
+    <t>Bom dia, Chamado para implementarmos melhorias no sistema de ACR. 1. Anexar análises de causa raiz junto aos pré formulários. 2. Identificar o tipo de gatilho no pré formulário 3. Melhorar resolução da tela de lista de causa raíz (está muito pequena) 4. Melhorar interface e interações para o usuário</t>
+  </si>
+  <si>
+    <t>12/05/2026</t>
+  </si>
+  <si>
+    <t>11665793630</t>
+  </si>
+  <si>
+    <t>Solicitação de melhoria no WMS – Pré-lista (EPI)</t>
+  </si>
+  <si>
+    <t>36624</t>
+  </si>
+  <si>
+    <t>Indicadores de retrabalho</t>
+  </si>
+  <si>
+    <t>Bom dia. Foi percebido diferen?as entre gr?ficos e dados nos indicadores abaixo. Favor verificar. No exemplo, foi filtrado os setores da KOMATSU. Selecionado o top 3 modelos com maior n?mero de horas em retrabalho. Ao extrair o excel, o total de horas ultrapassa significativamente a quantidade de ho</t>
+  </si>
+  <si>
+    <t>11688339983</t>
+  </si>
+  <si>
+    <t>Registro de solda Digital - Chamar consulta de cargas e sequencias</t>
+  </si>
+  <si>
+    <t>11688340260</t>
+  </si>
+  <si>
+    <t>Registro de solda Digital - Parametrizar telas para receber a sequencia</t>
+  </si>
+  <si>
+    <t>37682</t>
+  </si>
+  <si>
+    <t>Ordens corretivas em andamento</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito uma revisão no chamado 36705 para que busque apenas ordens corretivas no limite de ordens em aberto</t>
+  </si>
+  <si>
+    <t>Melhorias  no sistema de ACR - Excel ACR</t>
+  </si>
+  <si>
+    <t>11704959573</t>
+  </si>
+  <si>
+    <t>Flag Frete Próprio</t>
+  </si>
+  <si>
+    <t>09/04/2026</t>
+  </si>
+  <si>
+    <t>11704976254</t>
+  </si>
+  <si>
+    <t>Alerta Login CNPJ &lt;&gt; OC</t>
+  </si>
+  <si>
+    <t>37754</t>
+  </si>
+  <si>
+    <t>UPR</t>
+  </si>
+  <si>
+    <t>Criar terceiro como recurso</t>
+  </si>
+  <si>
+    <t>Boa tarde! Necessário incluir os terceiros como recurso, para poder sequenciar no APS. Obrigado! At.te,</t>
+  </si>
+  <si>
+    <t>Cristiano Nazário</t>
+  </si>
+  <si>
+    <t>11679618956</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Preparar Ambiente</t>
+  </si>
+  <si>
+    <t>Dashboard de Change Log - Governança de TI</t>
+  </si>
+  <si>
+    <t>Período</t>
+  </si>
+  <si>
+    <t>Out/2025</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Tickets corporativos para intranet / Power BI / Excel</t>
+  </si>
+  <si>
+    <t>Total de tickets</t>
+  </si>
+  <si>
+    <t>% dentro do SLA</t>
+  </si>
+  <si>
+    <t>Tempo médio (dias)</t>
+  </si>
+  <si>
+    <t>Áreas atendidas</t>
+  </si>
+  <si>
+    <t>Status final</t>
+  </si>
+  <si>
+    <t>Encerrado</t>
+  </si>
+  <si>
+    <t>Resumo Executivo</t>
+  </si>
+  <si>
+    <t>Tickets por Área</t>
+  </si>
+  <si>
+    <t>Distribuição por Tipo</t>
+  </si>
+  <si>
+    <t>Cumprimento SLA (15 dias)</t>
+  </si>
+  <si>
+    <t>Status Final</t>
+  </si>
+  <si>
+    <t>Tickets por Semana</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Muito Alta</t>
   </si>
   <si>
     <t>Sim</t>
-  </si>
-  <si>
-    <t>37461</t>
-  </si>
-  <si>
-    <t>Altona || Adiantamento de Clientes do Exterior - Relatório de Variação Cambial - (Reunião)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solicito a criação de uma rotina e posteriormente de um relatório que faça a demonstração da variação cambial dos adiantamentos de clientes do exterior. Para isso é preciso: 1) Criar um campo para cadastrar a moeda e sua respectiva cotação. Essa cotação será alimentada manualmente. Exemplo: Dólar – </t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>37475</t>
-  </si>
-  <si>
-    <t>BOTÃO ALTERAÇÃO DE TEMPO SIMULTÂNEA</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor criar um botão na tela UCPP11 que possibilite incluir o tempo em mais de um setor selecionado. OBS: Ideia alinhada com o Sr. Sandro Schram. Qualquer dúvida, estou à disposição. Obrigada, At.te</t>
-  </si>
-  <si>
-    <t>Karolina Moreira da Silva</t>
-  </si>
-  <si>
-    <t>36232</t>
-  </si>
-  <si>
-    <t>Report técnico - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
-  </si>
-  <si>
-    <t>33631</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - Custos</t>
-  </si>
-  <si>
-    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
-  </si>
-  <si>
-    <t>Marcelo Americo</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>30069</t>
-  </si>
-  <si>
-    <t>Controle de Importação - integração financeira</t>
-  </si>
-  <si>
-    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>36219</t>
-  </si>
-  <si>
-    <t>Melhoria Aplicação QlikSense - Custeio Horas</t>
-  </si>
-  <si>
-    <t>Felipe e Alexandre, bom dia! Gentileza desenvolverem QVD de extração de dados diretamente do Sistema de Custeio dos apontamentos de horas. Importar as planilhas Excel com ajustes gerenciais, para concatenar com informações base do Sistema.</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>Como teremos 3 modelagens as op’s poderão ter quantidades diferentes nas modelagens, validar com o pessoal do APS essa interligação.</t>
-  </si>
-  <si>
-    <t>36335</t>
-  </si>
-  <si>
-    <t>Ajuste em gráficos no B.I</t>
-  </si>
-  <si>
-    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
-  </si>
-  <si>
-    <t>36541</t>
-  </si>
-  <si>
-    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>36728</t>
-  </si>
-  <si>
-    <t>Aplicação QlikSense - Custeio FTF</t>
-  </si>
-  <si>
-    <t>Bom dia Felipe. Desenvolver um QVD para aplicação que possamos consultar custo FTF, semelhante informações do relatório FTF anexo.</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>37498</t>
-  </si>
-  <si>
-    <t>Alteração sistema registro USE-ULE Windows</t>
-  </si>
-  <si>
-    <t>Bom dia, Necessitamos que seja alterado a forma que os registros da moldagem são exibidos ao clicar no botão "Imprime Registro". Atualmente ao clicar no botão recebemos as informações com as respostas dos setores de preparação, moldagem, fechamento e desmoldagem, deixando de fora o setor da macharia</t>
-  </si>
-  <si>
-    <t>João Eduardo Zarth</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>37288</t>
-  </si>
-  <si>
-    <t>melhoria no sistema de inventário das embalagens</t>
-  </si>
-  <si>
-    <t>Bom dia! Com o aval do Rafael, solicito uma melhoria no sistema de inventário das embalagens (caixas Magayver). Atualmente, o sistema considera apenas as embalagens contadas fisicamente. Porém, existe a possibilidade de haver saldo no sistema mesmo quando a embalagem não existe fisicamente. Diante d</t>
-  </si>
-  <si>
-    <t>36430</t>
-  </si>
-  <si>
-    <t>Indicadores de Setup - IROG Usinagem</t>
-  </si>
-  <si>
-    <t>________________________________ De: Pedro Henrique Poburko Enviado: terça-feira, 3 de fevereiro de 2026 14:06 Para: Suporte Altona Assunto: RE: Resolvido: Indicadores de Setup - IROG Usinagem Felipe, bom dia. Precisamos que o tempo de entrega do indicador abaixo seja removido. Consegue alterar, por</t>
-  </si>
-  <si>
-    <t>Pedro Henrique Poburko</t>
-  </si>
-  <si>
-    <t>36218</t>
-  </si>
-  <si>
-    <t>Melhoria Aplicação QlikSense - Custeio Valor</t>
-  </si>
-  <si>
-    <t>Felipe bom dia! Importar para aplicação de Custeio planilhas Excel com a base de ajustes gerenciais, concatenando com o QVD de extração de dados diretamente do Sistema de Custeio.</t>
-  </si>
-  <si>
-    <t>37514</t>
-  </si>
-  <si>
-    <t>Melhoria cadastro de matérias</t>
-  </si>
-  <si>
-    <t>Boa tarde, Ao avaliar a plataforma, identifiquei a necessidade de algumas melhorias no sistema de cadastro de matérias: 1. Gostaria de solicitar a implementação de um campo no sistema que permita a geração de uma planilha em Excel antes da aprovação do cadastro. Att,</t>
-  </si>
-  <si>
-    <t>Vanessa Knoth</t>
-  </si>
-  <si>
-    <t>36206</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web (copy)</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>37526</t>
-  </si>
-  <si>
-    <t>PDI - Relatório de apontamentos</t>
-  </si>
-  <si>
-    <t>Verificar a situação apresentada pelo usuário Gerson Mendonça: Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Alexandre Longo</t>
-  </si>
-  <si>
-    <t>37499</t>
-  </si>
-  <si>
-    <t>Bom dia, Necessitamos que seja feita uma alteração no sistema de registro USE-ULE, precisamos que as imagens que ficam anexas as perguntas, quando exibidas pelo relatório do botão "Imprime Registro" sejam de um tamanho maior, que seja possível analisar de forma clara pelo computador. Sugerimos que s</t>
-  </si>
-  <si>
-    <t>Melhorias sistema de Tratamento Térmico - Checklist</t>
-  </si>
-  <si>
-    <t>36920</t>
-  </si>
-  <si>
-    <t>Link para vídeos</t>
-  </si>
-  <si>
-    <t>Bom dia, Estamos rodando o projeto de procedimentos por vídeos, necessitamos da criação de um link que possa ser acessado na aba documentos anexos dentro do sistema PCP, quando acessado o link, o colaborador assiste o vídeo que está no diretório, temos atualmente 10 vídeos para rodar o piloto. [Prec</t>
-  </si>
-  <si>
-    <t>Filipe Rosa</t>
-  </si>
-  <si>
-    <t>27/05/2026</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Tela apoio para forçar envio de dados.</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
-    <t>37200</t>
-  </si>
-  <si>
-    <t>Apontamento Escarfa - Apresentacao e acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos da elaboração de um sistema web para o corte escarfa UPR. São duas linhas apontadas por um operador simultaneamente (linha 1 e linha 2), Pra facilitar visual do operador e dinâmica dividir as duas linhas na mesma tela, mas com todos os resultados separados. As sequencias devem se</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>37450</t>
-  </si>
-  <si>
-    <t>NOVOS CAMPOS DE DESENHO NA AC E NO CPP</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor criar campos de desenhos conforme abaixo nas telas do CPP tanto de consulta [WWCPP221] quanto de manutenção [TTCPP], e no PCP tela de alteração de dados da análise crítica [TANCR011] (no PCP não há necessidade dos campos "3D"): Tela original: Tela proposta: Alterações: "Usinagem F."</t>
-  </si>
-  <si>
-    <t>37361</t>
-  </si>
-  <si>
-    <t>Base Histórica da Data de Reconhecimento  de Receita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
-  </si>
-  <si>
-    <t>Consulta log de registros.</t>
-  </si>
-  <si>
-    <t>36939</t>
-  </si>
-  <si>
-    <t>Usinagem</t>
-  </si>
-  <si>
-    <t>Incluir filtro "Select data range" - Usinagem IROG</t>
-  </si>
-  <si>
-    <t>Olá, Favor incluir o filtro "Select data range" na pasta principal da aplicação Usinagem IROG. Grato,</t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>36641</t>
-  </si>
-  <si>
-    <t>Sequencial number Clientes</t>
-  </si>
-  <si>
-    <t>36648</t>
-  </si>
-  <si>
-    <t>Causa Raiz - BI retrabalho TT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Precisamos incluir no banco de dados do BI do retrabalho de Tratamento Térmico a causa raiz do retrabalho. Essa informação é crucial para usar o BI de forma integral, sem necessidade de suporte de excel paralelo. Atualmente no excel tenho o banco de dados dessa maneira: DIA MÊS MÊS EXTENSO </t>
-  </si>
-  <si>
-    <t>Gilberto José Rebelo Junior</t>
-  </si>
-  <si>
-    <t>37412</t>
-  </si>
-  <si>
-    <t>Registro de Preset - Reunião</t>
-  </si>
-  <si>
-    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
-  </si>
-  <si>
-    <t>18/05/2026</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>37182</t>
-  </si>
-  <si>
-    <t>Análise</t>
-  </si>
-  <si>
-    <t>AJUSTES - EXTRAÇÃO DE DADOS APONTAMENTO LINHA MESAS REDONDAS (copy)</t>
-  </si>
-  <si>
-    <t>Bom dia, No dia 10/03/2026 iniciamos o piloto de apontamento eletrônico na linha mesas redondas, feito a extração em Excel notamos alguns pontos que precisam ser ajustados. * Coluna Y plan 1 (percentual executado) - puxando informações incorretas comparando com o que está sendo apontado no tablet. *</t>
-  </si>
-  <si>
-    <t>36777</t>
-  </si>
-  <si>
-    <t>Dúvida</t>
-  </si>
-  <si>
-    <t>Data de admissão</t>
-  </si>
-  <si>
-    <t>Bom dia. Adicionar coluna "data de admiss?o" nas informa??es de requisi??o de materiais</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
-    <t>Atualizar campos: data, hora e prazo da proposta</t>
-  </si>
-  <si>
-    <t>36381</t>
-  </si>
-  <si>
-    <t>58B4660910 - 407LX - Movimentação sem fluxo</t>
-  </si>
-  <si>
-    <t>Bom dia, Senhores, Poderiam verificar o que ocorreu aqui? Mesma sequ?ncia unit?ria colocada em 02 etiquetas com 4 min de diferen?a. Foi dado entrada como "sequ?ncia sem fluxo". Estamos com pendencia de 01 pe?a e o sistema n?o mostra isso hoje. Registro de entrada 2 etiquetas diferentes com a mesma s</t>
-  </si>
-  <si>
-    <t>32150</t>
-  </si>
-  <si>
-    <t>Inventario WMS - Registro de Ajuste de Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
-  </si>
-  <si>
-    <t>37485</t>
-  </si>
-  <si>
-    <t>opção de permissão</t>
-  </si>
-  <si>
-    <t>Boa tarde, Srs. Conforme falamos, a natureza do chamado tem como objetivo a solicitação de "permissão" para liderança da aciaria fazer movimentação as quais fogem do comum. Segue alguns exemplos abaixo: Onde fundimos 2 itens de ligas "Altona" diferentes 1304 e 1401. Onde não conseguimos baixar na co</t>
-  </si>
-  <si>
-    <t>Giancarlo Ibsch</t>
-  </si>
-  <si>
-    <t>31836</t>
-  </si>
-  <si>
-    <t>Melhoria WMS - Conferencia e Carregamento</t>
-  </si>
-  <si>
-    <t>36443</t>
-  </si>
-  <si>
-    <t>Problema</t>
-  </si>
-  <si>
-    <t>Falta dados - Aplicação Insertos Usinagem</t>
-  </si>
-  <si>
-    <t>Bom dia Felipe, Tudo certo? Favor verificar a aplicação de Insertos Usinagem, pois não está atualizando os dados desde o mês de outubro/2025. Uma aplicação que possui os dados da conta de insertos é a Consumo de Insumos e Materiais, porém não associa o modelo da peça e as máquinas da usinagem. Grato</t>
-  </si>
-  <si>
-    <t>32141</t>
-  </si>
-  <si>
-    <t>Cadastro de Embalagem no CPP</t>
-  </si>
-  <si>
-    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
-  </si>
-  <si>
-    <t>02/06/2026</t>
-  </si>
-  <si>
-    <t>37298</t>
-  </si>
-  <si>
-    <t>Melhoria | Custo de venda Orçamento Nacional</t>
-  </si>
-  <si>
-    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>ALTC - Verificar Retrabalho</t>
-  </si>
-  <si>
-    <t>37015</t>
-  </si>
-  <si>
-    <t>DIFA Interno e fretes - Ajuste de observação fiscal</t>
-  </si>
-  <si>
-    <t>Bom dia, Nas notas de DIFA interno e DIFA nos fretes precisa ser enviado os registros de observação fiscal e ajustes, conforme exemplo da NF 186758: O campo OBSERVACAO=@CODIGO(881) será o mesmo, o que vai mudar é o campo CODIGOAJUSTEBENEFICIO Nas notas de CFOP 1.556 e 1.551 o código de ajuste será S</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>36055</t>
-  </si>
-  <si>
-    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>36355</t>
-  </si>
-  <si>
-    <t>Alterar nome do filtro Ativo / Inativo para DESENV_ATIVOS e DESENV_INATIVOS</t>
-  </si>
-  <si>
-    <t>vide caminho para filtro no documento anexado.</t>
-  </si>
-  <si>
-    <t>36816</t>
-  </si>
-  <si>
-    <t>CRIAÇÃO DE B.I. PARA ACOMPANHAMENTO DE RESULTADOS DE ENSAIOS MECÂNICO - Reunião</t>
-  </si>
-  <si>
-    <t>23773</t>
-  </si>
-  <si>
-    <t>Registro de moldagem USE/ULE</t>
-  </si>
-  <si>
-    <t>Bom dia, Estamos tendo inconsistência nos registros de Moldagem USE/ULE, acontece às vezes do registro ser finalizado e a movimentação não ocorrer. Ocorre tanto na ULE como na USE. Exemplos abaixo: Duvidas entrar em contato. Att.</t>
-  </si>
-  <si>
-    <t>Darlan Pressi</t>
-  </si>
-  <si>
-    <t>36861</t>
-  </si>
-  <si>
-    <t>Aplicação de Solda</t>
-  </si>
-  <si>
-    <t>Bom dia, Gostaria de adicionar a informação do número do forno nesta tabela, ao lado da data de fusão. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Raiana Correa</t>
-  </si>
-  <si>
-    <t>37394</t>
-  </si>
-  <si>
-    <t>Rateio Jato Dirigido 1 e 2 - Fazer QG para atualizar operações na apon3 com base no estado da peça</t>
-  </si>
-  <si>
-    <t>Boa tarde, Hoje (20/03/26 ) foi criado as operações jato dirigido para cadastrarmos os tempos na CPP para rateio de tempo Qlik. Precisamos que esse rateio seja retroativo. No apontamento eletrônico o estado da peça era somente apontado para informação e não apontado sua real operação. Precisamos que</t>
-  </si>
-  <si>
-    <t>20/05/2026</t>
-  </si>
-  <si>
-    <t>33549</t>
-  </si>
-  <si>
-    <t>Integração de sistema Logística x data book - Relatório x Registro End's</t>
-  </si>
-  <si>
-    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
-  </si>
-  <si>
-    <t>Rosivaldo Silva</t>
-  </si>
-  <si>
-    <t>35808</t>
-  </si>
-  <si>
-    <t>Unificação de dados das aplicações de "Apontamento solda" x "Retrabalho Rebarbação</t>
-  </si>
-  <si>
-    <t>Bom dia! Percebi que não houve saída para abertura de um chamado sobre esta demanda "Unificação de dados das aplicações de "Apontamento solda" x "Retrabalho Rebarbação - item solda"" solicitada durante reuniões de meados de agosto e setembro/2025 conforme meus registros aqui. Solicito por aqui, entã</t>
-  </si>
-  <si>
-    <t>Cadastro de Embalagem no CPP (APS)</t>
-  </si>
-  <si>
-    <t>36885</t>
-  </si>
-  <si>
-    <t>Qualidade</t>
-  </si>
-  <si>
-    <t>Incluir o numero da nova revisão no alerta enviado pelo Posto de Cópias eletrônico</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos que seja incluído no alerta de revisão, o número da nova revisão dos documentos e também alguns ajustes. Abaixo segue um de exemplo: Hoje: Olá, Matheus Gonçalves, Já consta disponível no Sistema de Posto de Cópias Eletrônico nova revisão do documento IT 658 PROCESSO DE RECRUTAM</t>
-  </si>
-  <si>
-    <t>Matheus Gonçalves</t>
-  </si>
-  <si>
-    <t>32133</t>
-  </si>
-  <si>
-    <t>Novo Recurso</t>
-  </si>
-  <si>
-    <t>Automatização planilha comercial - PARTE 1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
-  </si>
-  <si>
-    <t>Jacson Schneider Movidesk</t>
-  </si>
-  <si>
-    <t>08/10/2025</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>34225</t>
-  </si>
-  <si>
-    <t>Correções Relatório Faturamento por Sequência - Acompanhamento (copy)</t>
-  </si>
-  <si>
-    <t>Sandro, bom dia! Solicito melhorias a seguir no Relatório Faturamento por Sequência. * Desconsiderar NF que não se tratam de venda (receita), por exemplo 210982/212675/213384/213385 (CFOP 5.949./6.949/7.949 - Remessa Conserto e Outros) NFe 213069 valor incorreto retornado no relatório.</t>
-  </si>
-  <si>
-    <t>36724</t>
-  </si>
-  <si>
-    <t>Alteração de registro de pintura</t>
-  </si>
-  <si>
-    <t>37190</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
-  </si>
-  <si>
-    <t>Guilherme Ferreira</t>
-  </si>
-  <si>
-    <t>19909</t>
-  </si>
-  <si>
-    <t>Criar KB Genexus especifica para Registro de pinturas</t>
-  </si>
-  <si>
-    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES (copy)</t>
-  </si>
-  <si>
-    <t>Revisar os campos: data, hora e prazo da proposta</t>
-  </si>
-  <si>
-    <t>37256</t>
-  </si>
-  <si>
-    <t>Melhoria no sistema de ACR</t>
-  </si>
-  <si>
-    <t>Bom dia, Chamado para implementarmos melhorias no sistema de ACR. 1. Anexar análises de causa raiz junto aos pré formulários. 2. Identificar o tipo de gatilho no pré formulário 3. Melhorar resolução da tela de lista de causa raíz (está muito pequena) 4. Melhorar interface e interações para o usuário</t>
-  </si>
-  <si>
-    <t>12/05/2026</t>
-  </si>
-  <si>
-    <t>35448</t>
-  </si>
-  <si>
-    <t>Solicitação de melhoria no WMS – Pré-lista (EPI)</t>
-  </si>
-  <si>
-    <t>36624</t>
-  </si>
-  <si>
-    <t>Indicadores de retrabalho</t>
-  </si>
-  <si>
-    <t>Bom dia. Foi percebido diferen?as entre gr?ficos e dados nos indicadores abaixo. Favor verificar. No exemplo, foi filtrado os setores da KOMATSU. Selecionado o top 3 modelos com maior n?mero de horas em retrabalho. Ao extrair o excel, o total de horas ultrapassa significativamente a quantidade de ho</t>
-  </si>
-  <si>
-    <t>37652</t>
-  </si>
-  <si>
-    <t>Registro de solda Digital - Chamar consulta de cargas e sequencias</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>Registro de solda Digital - Parametrizar telas para receber a sequencia</t>
-  </si>
-  <si>
-    <t>37682</t>
-  </si>
-  <si>
-    <t>Ordens corretivas em andamento</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito uma revisão no chamado 36705 para que busque apenas ordens corretivas no limite de ordens em aberto</t>
-  </si>
-  <si>
-    <t>Melhorias  no sistema de ACR - Excel ACR</t>
-  </si>
-  <si>
-    <t>08/04/2026</t>
-  </si>
-  <si>
-    <t>Flag Frete Próprio</t>
-  </si>
-  <si>
-    <t>Alerta Login CNPJ &lt;&gt; OC</t>
-  </si>
-  <si>
-    <t>37754</t>
-  </si>
-  <si>
-    <t>Criar terceiro como recurso</t>
-  </si>
-  <si>
-    <t>Boa tarde! Necessário incluir os terceiros como recurso, para poder sequenciar no APS. Obrigado! At.te,</t>
-  </si>
-  <si>
-    <t>Cristiano Nazário</t>
-  </si>
-  <si>
-    <t>36046</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Preparar Ambiente</t>
-  </si>
-  <si>
-    <t>Dashboard de Change Log - Governança de TI</t>
-  </si>
-  <si>
-    <t>Período</t>
-  </si>
-  <si>
-    <t>SPRINT 2026-11</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Tickets corporativos para intranet / Power BI / Excel</t>
-  </si>
-  <si>
-    <t>Total de tickets</t>
-  </si>
-  <si>
-    <t>% dentro do SLA</t>
-  </si>
-  <si>
-    <t>Tempo médio (dias)</t>
-  </si>
-  <si>
-    <t>Áreas atendidas</t>
-  </si>
-  <si>
-    <t>Status final</t>
-  </si>
-  <si>
-    <t>Encerrado</t>
-  </si>
-  <si>
-    <t>Resumo Executivo</t>
-  </si>
-  <si>
-    <t>Tickets por Área</t>
-  </si>
-  <si>
-    <t>Distribuição por Tipo</t>
-  </si>
-  <si>
-    <t>Cumprimento SLA (15 dias)</t>
-  </si>
-  <si>
-    <t>Status Final</t>
-  </si>
-  <si>
-    <t>Tickets por Semana</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Muito Alta</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1788,34 +1851,34 @@
         <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>26</v>
@@ -1824,7 +1887,7 @@
         <v>27</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>29</v>
@@ -1832,10 +1895,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
@@ -1844,16 +1907,16 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>23</v>
@@ -1879,10 +1942,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>17</v>
@@ -1891,34 +1954,34 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>29</v>
@@ -1926,10 +1989,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
@@ -1938,25 +2001,25 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>26</v>
@@ -1965,18 +2028,18 @@
         <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -1985,22 +2048,22 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>25</v>
@@ -2012,18 +2075,18 @@
         <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
@@ -2032,16 +2095,16 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>23</v>
@@ -2050,13 +2113,13 @@
         <v>24</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
@@ -2067,10 +2130,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
@@ -2079,45 +2142,45 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>17</v>
@@ -2126,16 +2189,16 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>23</v>
@@ -2161,10 +2224,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -2173,22 +2236,22 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>25</v>
@@ -2200,7 +2263,7 @@
         <v>27</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>29</v>
@@ -2208,10 +2271,10 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>17</v>
@@ -2220,22 +2283,22 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>25</v>
@@ -2247,7 +2310,7 @@
         <v>27</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>29</v>
@@ -2255,10 +2318,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>17</v>
@@ -2267,45 +2330,45 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>17</v>
@@ -2314,22 +2377,22 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>25</v>
@@ -2341,54 +2404,54 @@
         <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>29</v>
@@ -2396,104 +2459,104 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
@@ -2502,45 +2565,45 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>17</v>
@@ -2549,22 +2612,22 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>25</v>
@@ -2576,42 +2639,42 @@
         <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>25</v>
@@ -2623,18 +2686,18 @@
         <v>27</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>17</v>
@@ -2643,25 +2706,25 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>26</v>
@@ -2670,65 +2733,65 @@
         <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
@@ -2737,34 +2800,34 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>29</v>
@@ -2772,46 +2835,46 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>29</v>
@@ -2819,37 +2882,37 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>26</v>
@@ -2858,7 +2921,7 @@
         <v>27</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>29</v>
@@ -2866,37 +2929,37 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>26</v>
@@ -2905,7 +2968,7 @@
         <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>29</v>
@@ -2913,10 +2976,10 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>17</v>
@@ -2925,16 +2988,16 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>23</v>
@@ -2960,10 +3023,10 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
@@ -2972,34 +3035,34 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>29</v>
@@ -3007,10 +3070,10 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>17</v>
@@ -3019,22 +3082,22 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>25</v>
@@ -3046,7 +3109,7 @@
         <v>27</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>29</v>
@@ -3054,57 +3117,57 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>17</v>
@@ -3113,45 +3176,45 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>17</v>
@@ -3160,34 +3223,34 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>29</v>
@@ -3195,57 +3258,57 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>164</v>
+        <v>27</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>17</v>
@@ -3254,45 +3317,45 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>17</v>
@@ -3301,22 +3364,22 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>25</v>
@@ -3328,18 +3391,18 @@
         <v>27</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>17</v>
@@ -3348,25 +3411,25 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>26</v>
@@ -3375,18 +3438,18 @@
         <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>17</v>
@@ -3395,92 +3458,92 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
@@ -3489,34 +3552,34 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>29</v>
@@ -3524,10 +3587,10 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>17</v>
@@ -3536,34 +3599,34 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>29</v>
@@ -3571,10 +3634,10 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>17</v>
@@ -3583,92 +3646,92 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>16</v>
+        <v>204</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>34</v>
+        <v>207</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>17</v>
@@ -3677,22 +3740,22 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>25</v>
@@ -3707,15 +3770,15 @@
         <v>28</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>17</v>
@@ -3724,22 +3787,22 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>25</v>
@@ -3751,65 +3814,65 @@
         <v>27</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>17</v>
@@ -3818,22 +3881,22 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>25</v>
@@ -3845,15 +3908,15 @@
         <v>27</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3865,16 +3928,16 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>23</v>
@@ -3900,10 +3963,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
@@ -3912,22 +3975,22 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>25</v>
@@ -3939,7 +4002,7 @@
         <v>27</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>29</v>
@@ -3947,10 +4010,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>16</v>
+        <v>204</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
@@ -3959,22 +4022,22 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>25</v>
@@ -3986,65 +4049,65 @@
         <v>27</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
@@ -4053,45 +4116,45 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>229</v>
+        <v>142</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>17</v>
@@ -4100,45 +4163,45 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
@@ -4147,16 +4210,16 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>23</v>
@@ -4182,10 +4245,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
@@ -4194,25 +4257,25 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>26</v>
@@ -4221,7 +4284,7 @@
         <v>27</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>29</v>
@@ -4229,84 +4292,84 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>37</v>
+        <v>254</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>26</v>
@@ -4315,18 +4378,18 @@
         <v>27</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>17</v>
@@ -4335,22 +4398,22 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>25</v>
@@ -4362,18 +4425,18 @@
         <v>27</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>17</v>
@@ -4382,92 +4445,92 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>37</v>
+        <v>266</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>37</v>
+        <v>254</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>17</v>
@@ -4476,22 +4539,22 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>25</v>
@@ -4503,7 +4566,7 @@
         <v>27</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>29</v>
@@ -4511,40 +4574,40 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>37</v>
+        <v>274</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>27</v>
@@ -4553,15 +4616,15 @@
         <v>28</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>17</v>
@@ -4570,22 +4633,22 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>25</v>
@@ -4597,15 +4660,15 @@
         <v>27</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4617,13 +4680,13 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>22</v>
@@ -4632,10 +4695,10 @@
         <v>23</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>26</v>
@@ -4644,89 +4707,89 @@
         <v>27</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>25</v>
@@ -4738,42 +4801,42 @@
         <v>27</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>25</v>
@@ -4788,42 +4851,42 @@
         <v>28</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>37</v>
+        <v>254</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>37</v>
+        <v>266</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>26</v>
@@ -4832,45 +4895,45 @@
         <v>27</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>37</v>
+        <v>299</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>26</v>
@@ -4882,62 +4945,62 @@
         <v>28</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>17</v>
@@ -4946,22 +5009,22 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>25</v>
@@ -4973,45 +5036,45 @@
         <v>27</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>26</v>
@@ -5020,42 +5083,42 @@
         <v>27</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>25</v>
@@ -5070,42 +5133,42 @@
         <v>28</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>26</v>
@@ -5122,10 +5185,10 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>17</v>
@@ -5134,16 +5197,16 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>23</v>
@@ -5152,13 +5215,13 @@
         <v>24</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>28</v>
@@ -5169,37 +5232,37 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>26</v>
@@ -5208,18 +5271,18 @@
         <v>27</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>17</v>
@@ -5228,22 +5291,22 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>25</v>
@@ -5255,65 +5318,65 @@
         <v>27</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>17</v>
@@ -5322,22 +5385,22 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>25</v>
@@ -5352,42 +5415,42 @@
         <v>28</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>26</v>
@@ -5396,7 +5459,7 @@
         <v>27</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>29</v>
@@ -5404,34 +5467,34 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>25</v>
@@ -5443,42 +5506,42 @@
         <v>27</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>25</v>
@@ -5490,7 +5553,7 @@
         <v>27</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>29</v>
@@ -5498,10 +5561,10 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>17</v>
@@ -5510,45 +5573,45 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>17</v>
@@ -5557,45 +5620,45 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>17</v>
@@ -5604,25 +5667,25 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>26</v>
@@ -5631,65 +5694,65 @@
         <v>27</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>17</v>
@@ -5698,22 +5761,22 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>25</v>
@@ -5725,7 +5788,7 @@
         <v>27</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>29</v>
@@ -5733,57 +5796,57 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>16</v>
+        <v>195</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>17</v>
@@ -5792,22 +5855,22 @@
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>25</v>
@@ -5819,65 +5882,65 @@
         <v>27</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>17</v>
@@ -5886,16 +5949,16 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>23</v>
@@ -5904,13 +5967,13 @@
         <v>24</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>28</v>
@@ -5921,37 +5984,37 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>26</v>
@@ -5960,92 +6023,92 @@
         <v>27</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>101</v>
+        <v>377</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>104</v>
+        <v>378</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>37</v>
+        <v>274</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>27</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>37</v>
+        <v>254</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>26</v>
@@ -6054,18 +6117,18 @@
         <v>27</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>17</v>
@@ -6074,16 +6137,16 @@
         <v>18</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>23</v>
@@ -6092,7 +6155,7 @@
         <v>24</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>26</v>
@@ -6109,93 +6172,93 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O96" s="2" t="s">
         <v>29</v>
@@ -6203,84 +6266,84 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>374</v>
+        <v>147</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>37</v>
+        <v>274</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>374</v>
+        <v>147</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>26</v>
@@ -6289,18 +6352,18 @@
         <v>27</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>17</v>
@@ -6309,22 +6372,22 @@
         <v>18</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>374</v>
+        <v>147</v>
       </c>
       <c r="K99" s="2" t="s">
         <v>25</v>
@@ -6336,18 +6399,18 @@
         <v>27</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>17</v>
@@ -6356,25 +6419,25 @@
         <v>18</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>26</v>
@@ -6383,45 +6446,45 @@
         <v>27</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>129</v>
+        <v>397</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>37</v>
+        <v>399</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>26</v>
@@ -6430,45 +6493,45 @@
         <v>27</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>129</v>
+        <v>400</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>380</v>
+        <v>220</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>26</v>
@@ -6477,18 +6540,18 @@
         <v>27</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>17</v>
@@ -6497,22 +6560,22 @@
         <v>18</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>25</v>
@@ -6521,60 +6584,60 @@
         <v>26</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>164</v>
+        <v>27</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -6590,23 +6653,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B2" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="D2" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="E2" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6614,16 +6677,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6631,18 +6694,18 @@
         <v>103</v>
       </c>
       <c r="D5" s="5">
-        <v>0.029411764705882353</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>39.16</v>
+        <v>34.09</v>
       </c>
       <c r="J5" s="4">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6655,7 +6718,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K23">
         <v>10</v>
@@ -6663,7 +6726,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6694,12 +6757,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="B2">
         <v>103</v>
@@ -6707,49 +6770,49 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.029411764705882353</v>
+        <v>0</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>39.16</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -6758,16 +6821,16 @@
         <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>164</v>
+        <v>428</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>26</v>
@@ -6776,21 +6839,21 @@
         <v>58</v>
       </c>
       <c r="P10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q10">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -6805,48 +6868,48 @@
         <v>27</v>
       </c>
       <c r="K11">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="M11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N11">
         <v>23</v>
       </c>
       <c r="P11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>239</v>
+        <v>41</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="E12">
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12">
         <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="K12">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="N12">
         <v>4</v>
@@ -6855,62 +6918,62 @@
         <v>28</v>
       </c>
       <c r="Q12">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="P13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q13">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>116</v>
+        <v>236</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N14">
         <v>10</v>
@@ -6918,19 +6981,19 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -6938,13 +7001,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>254</v>
+        <v>53</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M16" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6952,13 +7015,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M17" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6966,18 +7029,30 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>339</v>
+        <v>195</v>
       </c>
       <c r="B18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
       <c r="D19" s="6" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -6985,150 +7060,192 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
       <c r="D21" s="2" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="F21" s="2">
-        <v>131</v>
+        <v>238</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="2">
+        <v>2</v>
+      </c>
       <c r="D22" s="2" t="s">
-        <v>233</v>
+        <v>91</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2">
-        <v>67</v>
+        <v>238</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2</v>
+      </c>
       <c r="D23" s="2" t="s">
-        <v>297</v>
+        <v>100</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F23" s="2">
-        <v>59</v>
+        <v>238</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
       <c r="D24" s="2" t="s">
-        <v>196</v>
+        <v>107</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F24" s="2">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
       <c r="D25" s="2" t="s">
-        <v>275</v>
+        <v>110</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="F25" s="2">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1</v>
+      </c>
       <c r="D26" s="2" t="s">
-        <v>293</v>
+        <v>130</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>254</v>
+        <v>31</v>
       </c>
       <c r="F26" s="2">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B27" s="2">
+        <v>1</v>
+      </c>
       <c r="D27" s="2" t="s">
-        <v>313</v>
+        <v>138</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="F27" s="2">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>314</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="F28" s="2">
-        <v>43</v>
+        <v>238</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>363</v>
+        <v>159</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2">
-        <v>38</v>
+        <v>238</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>364</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F30" s="2">
-        <v>33</v>
+        <v>238</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
